--- a/OUDSE2E/selenium-report.xlsx
+++ b/OUDSE2E/selenium-report.xlsx
@@ -4085,7 +4085,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4102,7 +4102,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4119,7 +4119,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4136,7 +4136,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4153,7 +4153,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4170,7 +4170,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4187,7 +4187,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4204,7 +4204,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4221,7 +4221,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4255,7 +4255,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4272,7 +4272,7 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4289,7 +4289,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4306,7 +4306,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4323,7 +4323,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4340,7 +4340,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4357,7 +4357,7 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4374,7 +4374,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4391,7 +4391,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4408,7 +4408,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4442,7 +4442,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -4459,7 +4459,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -4476,7 +4476,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -4493,7 +4493,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -4510,7 +4510,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4527,7 +4527,7 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4544,7 +4544,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -4578,7 +4578,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -4595,7 +4595,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -4612,7 +4612,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -4629,7 +4629,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -4646,7 +4646,7 @@
         <v>7</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4663,7 +4663,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -4680,7 +4680,7 @@
         <v>7</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -4714,7 +4714,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -4731,7 +4731,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4748,7 +4748,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -4765,7 +4765,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -4782,7 +4782,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -4799,7 +4799,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -4816,7 +4816,7 @@
         <v>7</v>
       </c>
       <c r="D45">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -4833,7 +4833,7 @@
         <v>7</v>
       </c>
       <c r="D46">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -4850,7 +4850,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -4884,7 +4884,7 @@
         <v>7</v>
       </c>
       <c r="D49">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -4901,7 +4901,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -4918,7 +4918,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -4969,7 +4969,7 @@
         <v>7</v>
       </c>
       <c r="D54">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -4986,7 +4986,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -5003,7 +5003,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5020,7 +5020,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5037,7 +5037,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -5054,7 +5054,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -5071,7 +5071,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -5088,7 +5088,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5105,7 +5105,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -5122,7 +5122,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -5139,7 +5139,7 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5156,7 +5156,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5173,7 +5173,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5190,7 +5190,7 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -5207,7 +5207,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5224,7 +5224,7 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -5241,7 +5241,7 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -5258,7 +5258,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5275,7 +5275,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5292,7 +5292,7 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>7</v>
       </c>
       <c r="D74">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -5326,7 +5326,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5343,7 +5343,7 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -5360,7 +5360,7 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5377,7 +5377,7 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5394,7 +5394,7 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -5428,7 +5428,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -5445,7 +5445,7 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5462,7 +5462,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -5479,7 +5479,7 @@
         <v>7</v>
       </c>
       <c r="D84">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -5496,7 +5496,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -5513,7 +5513,7 @@
         <v>7</v>
       </c>
       <c r="D86">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -5530,7 +5530,7 @@
         <v>7</v>
       </c>
       <c r="D87">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -5547,7 +5547,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -5564,7 +5564,7 @@
         <v>7</v>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -5598,7 +5598,7 @@
         <v>7</v>
       </c>
       <c r="D91">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -5615,7 +5615,7 @@
         <v>7</v>
       </c>
       <c r="D92">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -5632,7 +5632,7 @@
         <v>7</v>
       </c>
       <c r="D93">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5666,7 +5666,7 @@
         <v>7</v>
       </c>
       <c r="D95">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5683,7 +5683,7 @@
         <v>7</v>
       </c>
       <c r="D96">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="D97">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -5717,7 +5717,7 @@
         <v>7</v>
       </c>
       <c r="D98">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -5734,7 +5734,7 @@
         <v>7</v>
       </c>
       <c r="D99">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7</v>
       </c>
       <c r="D100">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -5768,7 +5768,7 @@
         <v>7</v>
       </c>
       <c r="D101">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -5785,7 +5785,7 @@
         <v>7</v>
       </c>
       <c r="D102">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -5802,7 +5802,7 @@
         <v>7</v>
       </c>
       <c r="D103">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -5819,7 +5819,7 @@
         <v>7</v>
       </c>
       <c r="D104">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -5836,7 +5836,7 @@
         <v>7</v>
       </c>
       <c r="D105">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -5853,7 +5853,7 @@
         <v>7</v>
       </c>
       <c r="D106">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -5870,7 +5870,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -5887,7 +5887,7 @@
         <v>7</v>
       </c>
       <c r="D108">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -5904,7 +5904,7 @@
         <v>7</v>
       </c>
       <c r="D109">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -5921,7 +5921,7 @@
         <v>7</v>
       </c>
       <c r="D110">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -5955,7 +5955,7 @@
         <v>7</v>
       </c>
       <c r="D112">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -5972,7 +5972,7 @@
         <v>7</v>
       </c>
       <c r="D113">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -5989,7 +5989,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6006,7 +6006,7 @@
         <v>7</v>
       </c>
       <c r="D115">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -6023,7 +6023,7 @@
         <v>7</v>
       </c>
       <c r="D116">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -6040,7 +6040,7 @@
         <v>7</v>
       </c>
       <c r="D117">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -6057,7 +6057,7 @@
         <v>7</v>
       </c>
       <c r="D118">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6074,7 +6074,7 @@
         <v>7</v>
       </c>
       <c r="D119">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6091,7 +6091,7 @@
         <v>7</v>
       </c>
       <c r="D120">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -6108,7 +6108,7 @@
         <v>7</v>
       </c>
       <c r="D121">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -6125,7 +6125,7 @@
         <v>7</v>
       </c>
       <c r="D122">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -6142,7 +6142,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6159,7 +6159,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6176,7 +6176,7 @@
         <v>7</v>
       </c>
       <c r="D125">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7</v>
       </c>
       <c r="D126">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -6210,7 +6210,7 @@
         <v>7</v>
       </c>
       <c r="D127">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6227,7 +6227,7 @@
         <v>7</v>
       </c>
       <c r="D128">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -6244,7 +6244,7 @@
         <v>7</v>
       </c>
       <c r="D129">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -6261,7 +6261,7 @@
         <v>7</v>
       </c>
       <c r="D130">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -6278,7 +6278,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -6295,7 +6295,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6312,7 +6312,7 @@
         <v>7</v>
       </c>
       <c r="D133">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -6329,7 +6329,7 @@
         <v>7</v>
       </c>
       <c r="D134">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -6346,7 +6346,7 @@
         <v>7</v>
       </c>
       <c r="D135">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6363,7 +6363,7 @@
         <v>7</v>
       </c>
       <c r="D136">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -6380,7 +6380,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -6397,7 +6397,7 @@
         <v>7</v>
       </c>
       <c r="D138">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -6414,7 +6414,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6431,7 +6431,7 @@
         <v>7</v>
       </c>
       <c r="D140">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -6448,7 +6448,7 @@
         <v>7</v>
       </c>
       <c r="D141">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -6465,7 +6465,7 @@
         <v>7</v>
       </c>
       <c r="D142">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6482,7 +6482,7 @@
         <v>7</v>
       </c>
       <c r="D143">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -6499,7 +6499,7 @@
         <v>7</v>
       </c>
       <c r="D144">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E144" t="s">
         <v>8</v>
@@ -6516,7 +6516,7 @@
         <v>7</v>
       </c>
       <c r="D145">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6533,7 +6533,7 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6550,7 +6550,7 @@
         <v>7</v>
       </c>
       <c r="D147">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -6567,7 +6567,7 @@
         <v>7</v>
       </c>
       <c r="D148">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -6584,7 +6584,7 @@
         <v>7</v>
       </c>
       <c r="D149">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6601,7 +6601,7 @@
         <v>7</v>
       </c>
       <c r="D150">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -6618,7 +6618,7 @@
         <v>7</v>
       </c>
       <c r="D151">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7</v>
       </c>
       <c r="D152">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -6652,7 +6652,7 @@
         <v>7</v>
       </c>
       <c r="D153">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6669,7 +6669,7 @@
         <v>7</v>
       </c>
       <c r="D154">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -6686,7 +6686,7 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -6703,7 +6703,7 @@
         <v>7</v>
       </c>
       <c r="D156">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -6720,7 +6720,7 @@
         <v>7</v>
       </c>
       <c r="D157">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -6737,7 +6737,7 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -6754,7 +6754,7 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6771,7 +6771,7 @@
         <v>7</v>
       </c>
       <c r="D160">
-        <v>7</v>
+        <v>295</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -6788,7 +6788,7 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -6805,7 +6805,7 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -6822,7 +6822,7 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -6839,7 +6839,7 @@
         <v>7</v>
       </c>
       <c r="D164">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -6856,7 +6856,7 @@
         <v>7</v>
       </c>
       <c r="D165">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -6873,7 +6873,7 @@
         <v>7</v>
       </c>
       <c r="D166">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -6890,7 +6890,7 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -6907,7 +6907,7 @@
         <v>7</v>
       </c>
       <c r="D168">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -6924,7 +6924,7 @@
         <v>7</v>
       </c>
       <c r="D169">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -6941,7 +6941,7 @@
         <v>7</v>
       </c>
       <c r="D170">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -6958,7 +6958,7 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -6975,7 +6975,7 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -6992,7 +6992,7 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7009,7 +7009,7 @@
         <v>7</v>
       </c>
       <c r="D174">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -7026,7 +7026,7 @@
         <v>7</v>
       </c>
       <c r="D175">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7043,7 +7043,7 @@
         <v>7</v>
       </c>
       <c r="D176">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -7060,7 +7060,7 @@
         <v>7</v>
       </c>
       <c r="D177">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>7</v>
       </c>
       <c r="D178">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7094,7 +7094,7 @@
         <v>7</v>
       </c>
       <c r="D179">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7111,7 +7111,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -7128,7 +7128,7 @@
         <v>7</v>
       </c>
       <c r="D181">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7145,7 +7145,7 @@
         <v>7</v>
       </c>
       <c r="D182">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7162,7 +7162,7 @@
         <v>7</v>
       </c>
       <c r="D183">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -7179,7 +7179,7 @@
         <v>7</v>
       </c>
       <c r="D184">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -7196,7 +7196,7 @@
         <v>7</v>
       </c>
       <c r="D185">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -7213,7 +7213,7 @@
         <v>7</v>
       </c>
       <c r="D186">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7230,7 +7230,7 @@
         <v>7</v>
       </c>
       <c r="D187">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -7247,7 +7247,7 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -7264,7 +7264,7 @@
         <v>7</v>
       </c>
       <c r="D189">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -7281,7 +7281,7 @@
         <v>7</v>
       </c>
       <c r="D190">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7298,7 +7298,7 @@
         <v>7</v>
       </c>
       <c r="D191">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -7315,7 +7315,7 @@
         <v>7</v>
       </c>
       <c r="D192">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -7332,7 +7332,7 @@
         <v>7</v>
       </c>
       <c r="D193">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -7349,7 +7349,7 @@
         <v>7</v>
       </c>
       <c r="D194">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -7366,7 +7366,7 @@
         <v>7</v>
       </c>
       <c r="D195">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7383,7 +7383,7 @@
         <v>7</v>
       </c>
       <c r="D196">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -7400,7 +7400,7 @@
         <v>7</v>
       </c>
       <c r="D197">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7417,7 +7417,7 @@
         <v>7</v>
       </c>
       <c r="D198">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E198" t="s">
         <v>8</v>
@@ -7434,7 +7434,7 @@
         <v>7</v>
       </c>
       <c r="D199">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -7451,7 +7451,7 @@
         <v>7</v>
       </c>
       <c r="D200">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -7468,7 +7468,7 @@
         <v>7</v>
       </c>
       <c r="D201">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -7485,7 +7485,7 @@
         <v>7</v>
       </c>
       <c r="D202">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -7502,7 +7502,7 @@
         <v>7</v>
       </c>
       <c r="D203">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7</v>
       </c>
       <c r="D204">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7536,7 +7536,7 @@
         <v>7</v>
       </c>
       <c r="D205">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -7553,7 +7553,7 @@
         <v>7</v>
       </c>
       <c r="D206">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7570,7 +7570,7 @@
         <v>7</v>
       </c>
       <c r="D207">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -7587,7 +7587,7 @@
         <v>7</v>
       </c>
       <c r="D208">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -7604,7 +7604,7 @@
         <v>7</v>
       </c>
       <c r="D209">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -7621,7 +7621,7 @@
         <v>7</v>
       </c>
       <c r="D210">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7638,7 +7638,7 @@
         <v>7</v>
       </c>
       <c r="D211">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -7655,7 +7655,7 @@
         <v>7</v>
       </c>
       <c r="D212">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -7672,7 +7672,7 @@
         <v>7</v>
       </c>
       <c r="D213">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7689,7 +7689,7 @@
         <v>7</v>
       </c>
       <c r="D214">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -7706,7 +7706,7 @@
         <v>7</v>
       </c>
       <c r="D215">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -7723,7 +7723,7 @@
         <v>7</v>
       </c>
       <c r="D216">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -7740,7 +7740,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -7757,7 +7757,7 @@
         <v>7</v>
       </c>
       <c r="D218">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -7774,7 +7774,7 @@
         <v>7</v>
       </c>
       <c r="D219">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -7791,7 +7791,7 @@
         <v>7</v>
       </c>
       <c r="D220">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -7808,7 +7808,7 @@
         <v>7</v>
       </c>
       <c r="D221">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -7825,7 +7825,7 @@
         <v>7</v>
       </c>
       <c r="D222">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -7842,7 +7842,7 @@
         <v>7</v>
       </c>
       <c r="D223">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -7859,7 +7859,7 @@
         <v>7</v>
       </c>
       <c r="D224">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -7876,7 +7876,7 @@
         <v>7</v>
       </c>
       <c r="D225">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -7893,7 +7893,7 @@
         <v>7</v>
       </c>
       <c r="D226">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -7910,7 +7910,7 @@
         <v>7</v>
       </c>
       <c r="D227">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -7927,7 +7927,7 @@
         <v>7</v>
       </c>
       <c r="D228">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -7944,7 +7944,7 @@
         <v>7</v>
       </c>
       <c r="D229">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>7</v>
       </c>
       <c r="D230">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -7978,7 +7978,7 @@
         <v>7</v>
       </c>
       <c r="D231">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -7995,7 +7995,7 @@
         <v>7</v>
       </c>
       <c r="D232">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -8012,7 +8012,7 @@
         <v>7</v>
       </c>
       <c r="D233">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -8029,7 +8029,7 @@
         <v>7</v>
       </c>
       <c r="D234">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -8046,7 +8046,7 @@
         <v>7</v>
       </c>
       <c r="D235">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -8063,7 +8063,7 @@
         <v>7</v>
       </c>
       <c r="D236">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -8080,7 +8080,7 @@
         <v>7</v>
       </c>
       <c r="D237">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -8097,7 +8097,7 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -8114,7 +8114,7 @@
         <v>7</v>
       </c>
       <c r="D239">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -8131,7 +8131,7 @@
         <v>7</v>
       </c>
       <c r="D240">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8148,7 +8148,7 @@
         <v>7</v>
       </c>
       <c r="D241">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -8165,7 +8165,7 @@
         <v>7</v>
       </c>
       <c r="D242">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8182,7 +8182,7 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -8199,7 +8199,7 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8216,7 +8216,7 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8233,7 +8233,7 @@
         <v>7</v>
       </c>
       <c r="D246">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -8250,7 +8250,7 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8267,7 +8267,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8284,7 +8284,7 @@
         <v>7</v>
       </c>
       <c r="D249">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -8301,7 +8301,7 @@
         <v>7</v>
       </c>
       <c r="D250">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -8318,7 +8318,7 @@
         <v>7</v>
       </c>
       <c r="D251">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8335,7 +8335,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8352,7 +8352,7 @@
         <v>7</v>
       </c>
       <c r="D253">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -8369,7 +8369,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -8386,7 +8386,7 @@
         <v>7</v>
       </c>
       <c r="D255">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>7</v>
       </c>
       <c r="D256">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -8420,7 +8420,7 @@
         <v>7</v>
       </c>
       <c r="D257">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -8437,7 +8437,7 @@
         <v>7</v>
       </c>
       <c r="D258">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8454,7 +8454,7 @@
         <v>7</v>
       </c>
       <c r="D259">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -8471,7 +8471,7 @@
         <v>7</v>
       </c>
       <c r="D260">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -8488,7 +8488,7 @@
         <v>7</v>
       </c>
       <c r="D261">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -8505,7 +8505,7 @@
         <v>7</v>
       </c>
       <c r="D262">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -8522,7 +8522,7 @@
         <v>7</v>
       </c>
       <c r="D263">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -8539,7 +8539,7 @@
         <v>7</v>
       </c>
       <c r="D264">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -8556,7 +8556,7 @@
         <v>7</v>
       </c>
       <c r="D265">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -8573,7 +8573,7 @@
         <v>7</v>
       </c>
       <c r="D266">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -8590,7 +8590,7 @@
         <v>7</v>
       </c>
       <c r="D267">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -8607,7 +8607,7 @@
         <v>7</v>
       </c>
       <c r="D268">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -8624,7 +8624,7 @@
         <v>7</v>
       </c>
       <c r="D269">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -8641,7 +8641,7 @@
         <v>7</v>
       </c>
       <c r="D270">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -8658,7 +8658,7 @@
         <v>7</v>
       </c>
       <c r="D271">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -8675,7 +8675,7 @@
         <v>7</v>
       </c>
       <c r="D272">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -8692,7 +8692,7 @@
         <v>7</v>
       </c>
       <c r="D273">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -8709,7 +8709,7 @@
         <v>7</v>
       </c>
       <c r="D274">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -8726,7 +8726,7 @@
         <v>7</v>
       </c>
       <c r="D275">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8743,7 +8743,7 @@
         <v>7</v>
       </c>
       <c r="D276">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8760,7 +8760,7 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -8777,7 +8777,7 @@
         <v>7</v>
       </c>
       <c r="D278">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -8794,7 +8794,7 @@
         <v>7</v>
       </c>
       <c r="D279">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -8811,7 +8811,7 @@
         <v>7</v>
       </c>
       <c r="D280">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -8828,7 +8828,7 @@
         <v>7</v>
       </c>
       <c r="D281">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7</v>
       </c>
       <c r="D282">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -8862,7 +8862,7 @@
         <v>7</v>
       </c>
       <c r="D283">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -8879,7 +8879,7 @@
         <v>7</v>
       </c>
       <c r="D284">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -8896,7 +8896,7 @@
         <v>7</v>
       </c>
       <c r="D285">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -8913,7 +8913,7 @@
         <v>7</v>
       </c>
       <c r="D286">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -8930,7 +8930,7 @@
         <v>7</v>
       </c>
       <c r="D287">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -8947,7 +8947,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -8964,7 +8964,7 @@
         <v>7</v>
       </c>
       <c r="D289">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -8981,7 +8981,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E290" t="s">
         <v>8</v>
@@ -8998,7 +8998,7 @@
         <v>7</v>
       </c>
       <c r="D291">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -9015,7 +9015,7 @@
         <v>7</v>
       </c>
       <c r="D292">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E292" t="s">
         <v>8</v>
@@ -9032,7 +9032,7 @@
         <v>7</v>
       </c>
       <c r="D293">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9049,7 +9049,7 @@
         <v>7</v>
       </c>
       <c r="D294">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -9066,7 +9066,7 @@
         <v>7</v>
       </c>
       <c r="D295">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -9083,7 +9083,7 @@
         <v>7</v>
       </c>
       <c r="D296">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9100,7 +9100,7 @@
         <v>7</v>
       </c>
       <c r="D297">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -9117,7 +9117,7 @@
         <v>7</v>
       </c>
       <c r="D298">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -9134,7 +9134,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9151,7 +9151,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9168,7 +9168,7 @@
         <v>7</v>
       </c>
       <c r="D301">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -9185,7 +9185,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9202,7 +9202,7 @@
         <v>7</v>
       </c>
       <c r="D303">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -9219,7 +9219,7 @@
         <v>7</v>
       </c>
       <c r="D304">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -9253,7 +9253,7 @@
         <v>7</v>
       </c>
       <c r="D306">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -9270,7 +9270,7 @@
         <v>7</v>
       </c>
       <c r="D307">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7</v>
       </c>
       <c r="D308">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -9304,7 +9304,7 @@
         <v>7</v>
       </c>
       <c r="D309">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -9321,7 +9321,7 @@
         <v>7</v>
       </c>
       <c r="D310">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -9338,7 +9338,7 @@
         <v>7</v>
       </c>
       <c r="D311">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9355,7 +9355,7 @@
         <v>7</v>
       </c>
       <c r="D312">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -9372,7 +9372,7 @@
         <v>7</v>
       </c>
       <c r="D313">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -9389,7 +9389,7 @@
         <v>7</v>
       </c>
       <c r="D314">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9406,7 +9406,7 @@
         <v>7</v>
       </c>
       <c r="D315">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9423,7 +9423,7 @@
         <v>7</v>
       </c>
       <c r="D316">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -9457,7 +9457,7 @@
         <v>7</v>
       </c>
       <c r="D318">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -9474,7 +9474,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9491,7 +9491,7 @@
         <v>7</v>
       </c>
       <c r="D320">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E320" t="s">
         <v>8</v>
@@ -9542,7 +9542,7 @@
         <v>7</v>
       </c>
       <c r="D323">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9559,7 +9559,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9576,7 +9576,7 @@
         <v>7</v>
       </c>
       <c r="D325">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9610,7 +9610,7 @@
         <v>7</v>
       </c>
       <c r="D327">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -9627,7 +9627,7 @@
         <v>7</v>
       </c>
       <c r="D328">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9644,7 +9644,7 @@
         <v>7</v>
       </c>
       <c r="D329">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -9661,7 +9661,7 @@
         <v>7</v>
       </c>
       <c r="D330">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -9678,7 +9678,7 @@
         <v>7</v>
       </c>
       <c r="D331">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -9695,7 +9695,7 @@
         <v>7</v>
       </c>
       <c r="D332">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -9712,7 +9712,7 @@
         <v>7</v>
       </c>
       <c r="D333">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -9746,7 +9746,7 @@
         <v>7</v>
       </c>
       <c r="D335">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -9763,7 +9763,7 @@
         <v>7</v>
       </c>
       <c r="D336">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -9780,7 +9780,7 @@
         <v>7</v>
       </c>
       <c r="D337">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -9797,7 +9797,7 @@
         <v>7</v>
       </c>
       <c r="D338">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -9814,7 +9814,7 @@
         <v>7</v>
       </c>
       <c r="D339">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -9831,7 +9831,7 @@
         <v>7</v>
       </c>
       <c r="D340">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -9848,7 +9848,7 @@
         <v>7</v>
       </c>
       <c r="D341">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -9865,7 +9865,7 @@
         <v>7</v>
       </c>
       <c r="D342">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -9899,7 +9899,7 @@
         <v>7</v>
       </c>
       <c r="D344">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -9916,7 +9916,7 @@
         <v>7</v>
       </c>
       <c r="D345">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -9933,7 +9933,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -9967,7 +9967,7 @@
         <v>7</v>
       </c>
       <c r="D348">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -10001,7 +10001,7 @@
         <v>7</v>
       </c>
       <c r="D350">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -10035,7 +10035,7 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -10086,7 +10086,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10103,7 +10103,7 @@
         <v>7</v>
       </c>
       <c r="D356">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -10120,7 +10120,7 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -10137,7 +10137,7 @@
         <v>7</v>
       </c>
       <c r="D358">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -10154,7 +10154,7 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -10188,7 +10188,7 @@
         <v>7</v>
       </c>
       <c r="D361">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -10205,7 +10205,7 @@
         <v>7</v>
       </c>
       <c r="D362">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -10222,7 +10222,7 @@
         <v>7</v>
       </c>
       <c r="D363">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -10256,7 +10256,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10273,7 +10273,7 @@
         <v>7</v>
       </c>
       <c r="D366">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10290,7 +10290,7 @@
         <v>7</v>
       </c>
       <c r="D367">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -10307,7 +10307,7 @@
         <v>7</v>
       </c>
       <c r="D368">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10324,7 +10324,7 @@
         <v>7</v>
       </c>
       <c r="D369">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -10341,7 +10341,7 @@
         <v>7</v>
       </c>
       <c r="D370">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -10358,7 +10358,7 @@
         <v>7</v>
       </c>
       <c r="D371">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10409,7 +10409,7 @@
         <v>7</v>
       </c>
       <c r="D374">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -10426,7 +10426,7 @@
         <v>7</v>
       </c>
       <c r="D375">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -10443,7 +10443,7 @@
         <v>7</v>
       </c>
       <c r="D376">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -10460,7 +10460,7 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -10477,7 +10477,7 @@
         <v>7</v>
       </c>
       <c r="D378">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -10494,7 +10494,7 @@
         <v>7</v>
       </c>
       <c r="D379">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -10511,7 +10511,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10528,7 +10528,7 @@
         <v>7</v>
       </c>
       <c r="D381">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -10545,7 +10545,7 @@
         <v>7</v>
       </c>
       <c r="D382">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -10562,7 +10562,7 @@
         <v>7</v>
       </c>
       <c r="D383">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E383" t="s">
         <v>8</v>
@@ -10579,7 +10579,7 @@
         <v>7</v>
       </c>
       <c r="D384">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -10596,7 +10596,7 @@
         <v>7</v>
       </c>
       <c r="D385">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>7</v>
       </c>
       <c r="D386">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -10630,7 +10630,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E387" t="s">
         <v>8</v>
@@ -10664,7 +10664,7 @@
         <v>7</v>
       </c>
       <c r="D389">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -10681,7 +10681,7 @@
         <v>7</v>
       </c>
       <c r="D390">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -10698,7 +10698,7 @@
         <v>7</v>
       </c>
       <c r="D391">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10732,7 +10732,7 @@
         <v>7</v>
       </c>
       <c r="D393">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E393" t="s">
         <v>8</v>
@@ -10766,7 +10766,7 @@
         <v>7</v>
       </c>
       <c r="D395">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E395" t="s">
         <v>8</v>
@@ -10783,7 +10783,7 @@
         <v>7</v>
       </c>
       <c r="D396">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E396" t="s">
         <v>8</v>
@@ -10817,7 +10817,7 @@
         <v>7</v>
       </c>
       <c r="D398">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -10868,7 +10868,7 @@
         <v>7</v>
       </c>
       <c r="D401">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E401" t="s">
         <v>8</v>
@@ -10885,7 +10885,7 @@
         <v>7</v>
       </c>
       <c r="D402">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E402" t="s">
         <v>8</v>
@@ -10902,7 +10902,7 @@
         <v>7</v>
       </c>
       <c r="D403">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E403" t="s">
         <v>8</v>
@@ -10953,7 +10953,7 @@
         <v>7</v>
       </c>
       <c r="D406">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E406" t="s">
         <v>8</v>
@@ -10970,7 +10970,7 @@
         <v>7</v>
       </c>
       <c r="D407">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E407" t="s">
         <v>8</v>
@@ -11004,7 +11004,7 @@
         <v>7</v>
       </c>
       <c r="D409">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E409" t="s">
         <v>8</v>
@@ -11021,7 +11021,7 @@
         <v>7</v>
       </c>
       <c r="D410">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>7</v>
       </c>
       <c r="D412">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E412" t="s">
         <v>8</v>
@@ -11072,7 +11072,7 @@
         <v>7</v>
       </c>
       <c r="D413">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E413" t="s">
         <v>8</v>
@@ -11089,7 +11089,7 @@
         <v>7</v>
       </c>
       <c r="D414">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E414" t="s">
         <v>8</v>
@@ -11123,7 +11123,7 @@
         <v>7</v>
       </c>
       <c r="D416">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11140,7 +11140,7 @@
         <v>7</v>
       </c>
       <c r="D417">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E417" t="s">
         <v>8</v>
@@ -11157,7 +11157,7 @@
         <v>7</v>
       </c>
       <c r="D418">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E418" t="s">
         <v>8</v>
@@ -11174,7 +11174,7 @@
         <v>7</v>
       </c>
       <c r="D419">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E419" t="s">
         <v>8</v>
@@ -11191,7 +11191,7 @@
         <v>7</v>
       </c>
       <c r="D420">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E420" t="s">
         <v>8</v>
@@ -11208,7 +11208,7 @@
         <v>7</v>
       </c>
       <c r="D421">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E421" t="s">
         <v>8</v>
@@ -11242,7 +11242,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11259,7 +11259,7 @@
         <v>7</v>
       </c>
       <c r="D424">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E424" t="s">
         <v>8</v>
@@ -11276,7 +11276,7 @@
         <v>7</v>
       </c>
       <c r="D425">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11310,7 +11310,7 @@
         <v>7</v>
       </c>
       <c r="D427">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11327,7 +11327,7 @@
         <v>7</v>
       </c>
       <c r="D428">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E428" t="s">
         <v>8</v>
@@ -11344,7 +11344,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E429" t="s">
         <v>8</v>
@@ -11361,7 +11361,7 @@
         <v>7</v>
       </c>
       <c r="D430">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E430" t="s">
         <v>8</v>
@@ -11378,7 +11378,7 @@
         <v>7</v>
       </c>
       <c r="D431">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11412,7 +11412,7 @@
         <v>7</v>
       </c>
       <c r="D433">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E433" t="s">
         <v>8</v>
@@ -11429,7 +11429,7 @@
         <v>7</v>
       </c>
       <c r="D434">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E434" t="s">
         <v>8</v>
@@ -11446,7 +11446,7 @@
         <v>7</v>
       </c>
       <c r="D435">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E435" t="s">
         <v>8</v>
@@ -11463,7 +11463,7 @@
         <v>7</v>
       </c>
       <c r="D436">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E436" t="s">
         <v>8</v>
@@ -11480,7 +11480,7 @@
         <v>7</v>
       </c>
       <c r="D437">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E437" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>7</v>
       </c>
       <c r="D438">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E438" t="s">
         <v>8</v>
@@ -11514,7 +11514,7 @@
         <v>7</v>
       </c>
       <c r="D439">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11531,7 +11531,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11548,7 +11548,7 @@
         <v>7</v>
       </c>
       <c r="D441">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E441" t="s">
         <v>8</v>
@@ -11565,7 +11565,7 @@
         <v>7</v>
       </c>
       <c r="D442">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E442" t="s">
         <v>8</v>
@@ -11582,7 +11582,7 @@
         <v>7</v>
       </c>
       <c r="D443">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E443" t="s">
         <v>8</v>
@@ -11599,7 +11599,7 @@
         <v>7</v>
       </c>
       <c r="D444">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E444" t="s">
         <v>8</v>
@@ -11616,7 +11616,7 @@
         <v>7</v>
       </c>
       <c r="D445">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E445" t="s">
         <v>8</v>
@@ -11633,7 +11633,7 @@
         <v>7</v>
       </c>
       <c r="D446">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E446" t="s">
         <v>8</v>
@@ -11650,7 +11650,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E447" t="s">
         <v>8</v>
@@ -11667,7 +11667,7 @@
         <v>7</v>
       </c>
       <c r="D448">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11684,7 +11684,7 @@
         <v>7</v>
       </c>
       <c r="D449">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11701,7 +11701,7 @@
         <v>7</v>
       </c>
       <c r="D450">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E450" t="s">
         <v>8</v>
@@ -11718,7 +11718,7 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E451" t="s">
         <v>8</v>
@@ -11735,7 +11735,7 @@
         <v>7</v>
       </c>
       <c r="D452">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11752,7 +11752,7 @@
         <v>7</v>
       </c>
       <c r="D453">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E453" t="s">
         <v>8</v>
@@ -11769,7 +11769,7 @@
         <v>7</v>
       </c>
       <c r="D454">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E454" t="s">
         <v>8</v>
@@ -11786,7 +11786,7 @@
         <v>7</v>
       </c>
       <c r="D455">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E455" t="s">
         <v>8</v>
@@ -11803,7 +11803,7 @@
         <v>7</v>
       </c>
       <c r="D456">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E456" t="s">
         <v>8</v>
@@ -11837,7 +11837,7 @@
         <v>7</v>
       </c>
       <c r="D458">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E458" t="s">
         <v>8</v>
@@ -11854,7 +11854,7 @@
         <v>7</v>
       </c>
       <c r="D459">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E459" t="s">
         <v>8</v>
@@ -11871,7 +11871,7 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E460" t="s">
         <v>8</v>
@@ -11888,7 +11888,7 @@
         <v>7</v>
       </c>
       <c r="D461">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -11905,7 +11905,7 @@
         <v>7</v>
       </c>
       <c r="D462">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E462" t="s">
         <v>8</v>
@@ -11922,7 +11922,7 @@
         <v>7</v>
       </c>
       <c r="D463">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E463" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7</v>
       </c>
       <c r="D464">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E464" t="s">
         <v>8</v>
@@ -11973,7 +11973,7 @@
         <v>7</v>
       </c>
       <c r="D466">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E466" t="s">
         <v>8</v>
@@ -11990,7 +11990,7 @@
         <v>7</v>
       </c>
       <c r="D467">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E467" t="s">
         <v>8</v>
@@ -12007,7 +12007,7 @@
         <v>7</v>
       </c>
       <c r="D468">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E468" t="s">
         <v>8</v>
@@ -12041,7 +12041,7 @@
         <v>7</v>
       </c>
       <c r="D470">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E470" t="s">
         <v>8</v>
@@ -12075,7 +12075,7 @@
         <v>7</v>
       </c>
       <c r="D472">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E472" t="s">
         <v>8</v>
@@ -12092,7 +12092,7 @@
         <v>7</v>
       </c>
       <c r="D473">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E473" t="s">
         <v>8</v>
@@ -12109,7 +12109,7 @@
         <v>7</v>
       </c>
       <c r="D474">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12126,7 +12126,7 @@
         <v>7</v>
       </c>
       <c r="D475">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E475" t="s">
         <v>8</v>
@@ -12160,7 +12160,7 @@
         <v>7</v>
       </c>
       <c r="D477">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12194,7 +12194,7 @@
         <v>7</v>
       </c>
       <c r="D479">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E479" t="s">
         <v>8</v>
@@ -12228,7 +12228,7 @@
         <v>7</v>
       </c>
       <c r="D481">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E481" t="s">
         <v>8</v>
@@ -12262,7 +12262,7 @@
         <v>7</v>
       </c>
       <c r="D483">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E483" t="s">
         <v>8</v>
@@ -12296,7 +12296,7 @@
         <v>7</v>
       </c>
       <c r="D485">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E485" t="s">
         <v>8</v>
@@ -12313,7 +12313,7 @@
         <v>7</v>
       </c>
       <c r="D486">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E486" t="s">
         <v>8</v>
@@ -12330,7 +12330,7 @@
         <v>7</v>
       </c>
       <c r="D487">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E487" t="s">
         <v>8</v>
@@ -12364,7 +12364,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E489" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>7</v>
       </c>
       <c r="D490">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E490" t="s">
         <v>8</v>
@@ -12398,7 +12398,7 @@
         <v>7</v>
       </c>
       <c r="D491">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E491" t="s">
         <v>8</v>
@@ -12449,7 +12449,7 @@
         <v>7</v>
       </c>
       <c r="D494">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E494" t="s">
         <v>8</v>
@@ -12466,7 +12466,7 @@
         <v>7</v>
       </c>
       <c r="D495">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E495" t="s">
         <v>8</v>
@@ -12483,7 +12483,7 @@
         <v>7</v>
       </c>
       <c r="D496">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E496" t="s">
         <v>8</v>
@@ -12534,7 +12534,7 @@
         <v>7</v>
       </c>
       <c r="D499">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E499" t="s">
         <v>8</v>
@@ -12551,7 +12551,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E500" t="s">
         <v>8</v>
@@ -12585,7 +12585,7 @@
         <v>7</v>
       </c>
       <c r="D502">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E502" t="s">
         <v>8</v>
@@ -12602,7 +12602,7 @@
         <v>7</v>
       </c>
       <c r="D503">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E503" t="s">
         <v>8</v>
@@ -12619,7 +12619,7 @@
         <v>7</v>
       </c>
       <c r="D504">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12636,7 +12636,7 @@
         <v>7</v>
       </c>
       <c r="D505">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12653,7 +12653,7 @@
         <v>7</v>
       </c>
       <c r="D506">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E506" t="s">
         <v>8</v>
@@ -12670,7 +12670,7 @@
         <v>7</v>
       </c>
       <c r="D507">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E507" t="s">
         <v>8</v>
@@ -12704,7 +12704,7 @@
         <v>7</v>
       </c>
       <c r="D509">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E509" t="s">
         <v>8</v>
@@ -12721,7 +12721,7 @@
         <v>7</v>
       </c>
       <c r="D510">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E510" t="s">
         <v>8</v>
@@ -12738,7 +12738,7 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E511" t="s">
         <v>8</v>
@@ -12755,7 +12755,7 @@
         <v>7</v>
       </c>
       <c r="D512">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E512" t="s">
         <v>8</v>
@@ -12772,7 +12772,7 @@
         <v>7</v>
       </c>
       <c r="D513">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E513" t="s">
         <v>8</v>
@@ -12806,7 +12806,7 @@
         <v>7</v>
       </c>
       <c r="D515">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E515" t="s">
         <v>8</v>
@@ -12874,7 +12874,7 @@
         <v>7</v>
       </c>
       <c r="D519">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E519" t="s">
         <v>8</v>
@@ -12942,7 +12942,7 @@
         <v>7</v>
       </c>
       <c r="D523">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E523" t="s">
         <v>8</v>
@@ -12976,7 +12976,7 @@
         <v>7</v>
       </c>
       <c r="D525">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E525" t="s">
         <v>8</v>
@@ -12993,7 +12993,7 @@
         <v>7</v>
       </c>
       <c r="D526">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E526" t="s">
         <v>8</v>
@@ -13010,7 +13010,7 @@
         <v>7</v>
       </c>
       <c r="D527">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E527" t="s">
         <v>8</v>
@@ -13027,7 +13027,7 @@
         <v>7</v>
       </c>
       <c r="D528">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E528" t="s">
         <v>8</v>
@@ -13061,7 +13061,7 @@
         <v>7</v>
       </c>
       <c r="D530">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E530" t="s">
         <v>8</v>
@@ -13078,7 +13078,7 @@
         <v>7</v>
       </c>
       <c r="D531">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E531" t="s">
         <v>8</v>
@@ -13095,7 +13095,7 @@
         <v>7</v>
       </c>
       <c r="D532">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13112,7 +13112,7 @@
         <v>7</v>
       </c>
       <c r="D533">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13146,7 +13146,7 @@
         <v>7</v>
       </c>
       <c r="D535">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13163,7 +13163,7 @@
         <v>7</v>
       </c>
       <c r="D536">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13180,7 +13180,7 @@
         <v>7</v>
       </c>
       <c r="D537">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
@@ -13197,7 +13197,7 @@
         <v>7</v>
       </c>
       <c r="D538">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E538" t="s">
         <v>8</v>
@@ -13214,7 +13214,7 @@
         <v>7</v>
       </c>
       <c r="D539">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E539" t="s">
         <v>8</v>
@@ -13231,7 +13231,7 @@
         <v>7</v>
       </c>
       <c r="D540">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E540" t="s">
         <v>8</v>
@@ -13248,7 +13248,7 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E541" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>7</v>
       </c>
       <c r="D542">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E542" t="s">
         <v>8</v>
@@ -13299,7 +13299,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E544" t="s">
         <v>8</v>
@@ -13316,7 +13316,7 @@
         <v>7</v>
       </c>
       <c r="D545">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E545" t="s">
         <v>8</v>
@@ -13333,7 +13333,7 @@
         <v>7</v>
       </c>
       <c r="D546">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E546" t="s">
         <v>8</v>
@@ -13350,7 +13350,7 @@
         <v>7</v>
       </c>
       <c r="D547">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E547" t="s">
         <v>8</v>
@@ -13367,7 +13367,7 @@
         <v>7</v>
       </c>
       <c r="D548">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E548" t="s">
         <v>8</v>
@@ -13384,7 +13384,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E549" t="s">
         <v>8</v>
@@ -13401,7 +13401,7 @@
         <v>7</v>
       </c>
       <c r="D550">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E550" t="s">
         <v>8</v>
@@ -13418,7 +13418,7 @@
         <v>7</v>
       </c>
       <c r="D551">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="E551" t="s">
         <v>8</v>
@@ -13435,7 +13435,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="E552" t="s">
         <v>8</v>
@@ -13452,7 +13452,7 @@
         <v>7</v>
       </c>
       <c r="D553">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E553" t="s">
         <v>8</v>
@@ -13469,7 +13469,7 @@
         <v>7</v>
       </c>
       <c r="D554">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E554" t="s">
         <v>8</v>
@@ -13486,7 +13486,7 @@
         <v>7</v>
       </c>
       <c r="D555">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E555" t="s">
         <v>8</v>
@@ -13503,7 +13503,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E556" t="s">
         <v>8</v>
@@ -13520,7 +13520,7 @@
         <v>7</v>
       </c>
       <c r="D557">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E557" t="s">
         <v>8</v>
@@ -13537,7 +13537,7 @@
         <v>7</v>
       </c>
       <c r="D558">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E558" t="s">
         <v>8</v>
@@ -13554,7 +13554,7 @@
         <v>7</v>
       </c>
       <c r="D559">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E559" t="s">
         <v>8</v>
@@ -13588,7 +13588,7 @@
         <v>7</v>
       </c>
       <c r="D561">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E561" t="s">
         <v>8</v>
@@ -13605,7 +13605,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E562" t="s">
         <v>8</v>
@@ -13622,7 +13622,7 @@
         <v>7</v>
       </c>
       <c r="D563">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="E563" t="s">
         <v>8</v>
@@ -13639,7 +13639,7 @@
         <v>7</v>
       </c>
       <c r="D564">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E564" t="s">
         <v>8</v>
@@ -13656,7 +13656,7 @@
         <v>7</v>
       </c>
       <c r="D565">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E565" t="s">
         <v>8</v>
@@ -13673,7 +13673,7 @@
         <v>7</v>
       </c>
       <c r="D566">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E566" t="s">
         <v>8</v>
@@ -13690,7 +13690,7 @@
         <v>7</v>
       </c>
       <c r="D567">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E567" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>7</v>
       </c>
       <c r="D568">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E568" t="s">
         <v>8</v>
@@ -13724,7 +13724,7 @@
         <v>7</v>
       </c>
       <c r="D569">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E569" t="s">
         <v>8</v>
@@ -13741,7 +13741,7 @@
         <v>7</v>
       </c>
       <c r="D570">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E570" t="s">
         <v>8</v>
@@ -13758,7 +13758,7 @@
         <v>7</v>
       </c>
       <c r="D571">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E571" t="s">
         <v>8</v>
@@ -13775,7 +13775,7 @@
         <v>7</v>
       </c>
       <c r="D572">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E572" t="s">
         <v>8</v>
@@ -13792,7 +13792,7 @@
         <v>7</v>
       </c>
       <c r="D573">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E573" t="s">
         <v>8</v>
@@ -13809,7 +13809,7 @@
         <v>7</v>
       </c>
       <c r="D574">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E574" t="s">
         <v>8</v>
@@ -13826,7 +13826,7 @@
         <v>7</v>
       </c>
       <c r="D575">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E575" t="s">
         <v>8</v>
@@ -13843,7 +13843,7 @@
         <v>7</v>
       </c>
       <c r="D576">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E576" t="s">
         <v>8</v>
@@ -13860,7 +13860,7 @@
         <v>7</v>
       </c>
       <c r="D577">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E577" t="s">
         <v>8</v>
@@ -13877,7 +13877,7 @@
         <v>7</v>
       </c>
       <c r="D578">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E578" t="s">
         <v>8</v>
@@ -13894,7 +13894,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E579" t="s">
         <v>8</v>
@@ -13911,7 +13911,7 @@
         <v>7</v>
       </c>
       <c r="D580">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E580" t="s">
         <v>8</v>
@@ -13928,7 +13928,7 @@
         <v>7</v>
       </c>
       <c r="D581">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E581" t="s">
         <v>8</v>
@@ -13945,7 +13945,7 @@
         <v>7</v>
       </c>
       <c r="D582">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E582" t="s">
         <v>8</v>
@@ -13979,7 +13979,7 @@
         <v>7</v>
       </c>
       <c r="D584">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E584" t="s">
         <v>8</v>
@@ -14013,7 +14013,7 @@
         <v>7</v>
       </c>
       <c r="D586">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E586" t="s">
         <v>8</v>
@@ -14030,7 +14030,7 @@
         <v>7</v>
       </c>
       <c r="D587">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E587" t="s">
         <v>8</v>
@@ -14064,7 +14064,7 @@
         <v>7</v>
       </c>
       <c r="D589">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E589" t="s">
         <v>8</v>
@@ -14098,7 +14098,7 @@
         <v>7</v>
       </c>
       <c r="D591">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E591" t="s">
         <v>8</v>
@@ -14115,7 +14115,7 @@
         <v>7</v>
       </c>
       <c r="D592">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E592" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7</v>
       </c>
       <c r="D594">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E594" t="s">
         <v>8</v>
@@ -14200,7 +14200,7 @@
         <v>7</v>
       </c>
       <c r="D597">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E597" t="s">
         <v>8</v>
@@ -14234,7 +14234,7 @@
         <v>7</v>
       </c>
       <c r="D599">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E599" t="s">
         <v>8</v>
@@ -14251,7 +14251,7 @@
         <v>7</v>
       </c>
       <c r="D600">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E600" t="s">
         <v>8</v>
@@ -14268,7 +14268,7 @@
         <v>7</v>
       </c>
       <c r="D601">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E601" t="s">
         <v>8</v>
@@ -14285,7 +14285,7 @@
         <v>7</v>
       </c>
       <c r="D602">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E602" t="s">
         <v>8</v>
@@ -14302,7 +14302,7 @@
         <v>7</v>
       </c>
       <c r="D603">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E603" t="s">
         <v>8</v>
@@ -14319,7 +14319,7 @@
         <v>7</v>
       </c>
       <c r="D604">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E604" t="s">
         <v>8</v>
@@ -14353,7 +14353,7 @@
         <v>7</v>
       </c>
       <c r="D606">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E606" t="s">
         <v>8</v>
@@ -14370,7 +14370,7 @@
         <v>7</v>
       </c>
       <c r="D607">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E607" t="s">
         <v>8</v>
@@ -14387,7 +14387,7 @@
         <v>7</v>
       </c>
       <c r="D608">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E608" t="s">
         <v>8</v>
@@ -14421,7 +14421,7 @@
         <v>7</v>
       </c>
       <c r="D610">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E610" t="s">
         <v>8</v>
@@ -14455,7 +14455,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E612" t="s">
         <v>8</v>
@@ -14472,7 +14472,7 @@
         <v>7</v>
       </c>
       <c r="D613">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E613" t="s">
         <v>8</v>
@@ -14523,7 +14523,7 @@
         <v>7</v>
       </c>
       <c r="D616">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E616" t="s">
         <v>8</v>
@@ -14540,7 +14540,7 @@
         <v>7</v>
       </c>
       <c r="D617">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E617" t="s">
         <v>8</v>
@@ -14574,7 +14574,7 @@
         <v>7</v>
       </c>
       <c r="D619">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E619" t="s">
         <v>8</v>
@@ -14608,7 +14608,7 @@
         <v>7</v>
       </c>
       <c r="D621">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E621" t="s">
         <v>8</v>
@@ -14625,7 +14625,7 @@
         <v>7</v>
       </c>
       <c r="D622">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E622" t="s">
         <v>8</v>
@@ -14659,7 +14659,7 @@
         <v>7</v>
       </c>
       <c r="D624">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E624" t="s">
         <v>8</v>
@@ -14676,7 +14676,7 @@
         <v>7</v>
       </c>
       <c r="D625">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E625" t="s">
         <v>8</v>
@@ -14693,7 +14693,7 @@
         <v>7</v>
       </c>
       <c r="D626">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E626" t="s">
         <v>8</v>
@@ -14710,7 +14710,7 @@
         <v>7</v>
       </c>
       <c r="D627">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E627" t="s">
         <v>8</v>
@@ -14727,7 +14727,7 @@
         <v>7</v>
       </c>
       <c r="D628">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E628" t="s">
         <v>8</v>
@@ -14761,7 +14761,7 @@
         <v>7</v>
       </c>
       <c r="D630">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E630" t="s">
         <v>8</v>
@@ -14778,7 +14778,7 @@
         <v>7</v>
       </c>
       <c r="D631">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E631" t="s">
         <v>8</v>
@@ -14795,7 +14795,7 @@
         <v>7</v>
       </c>
       <c r="D632">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E632" t="s">
         <v>8</v>
@@ -14812,7 +14812,7 @@
         <v>7</v>
       </c>
       <c r="D633">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E633" t="s">
         <v>8</v>
@@ -14846,7 +14846,7 @@
         <v>7</v>
       </c>
       <c r="D635">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E635" t="s">
         <v>8</v>
@@ -14863,7 +14863,7 @@
         <v>7</v>
       </c>
       <c r="D636">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E636" t="s">
         <v>8</v>
@@ -14880,7 +14880,7 @@
         <v>7</v>
       </c>
       <c r="D637">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E637" t="s">
         <v>8</v>
@@ -14914,7 +14914,7 @@
         <v>7</v>
       </c>
       <c r="D639">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E639" t="s">
         <v>8</v>
@@ -14948,7 +14948,7 @@
         <v>7</v>
       </c>
       <c r="D641">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E641" t="s">
         <v>8</v>
@@ -14999,7 +14999,7 @@
         <v>7</v>
       </c>
       <c r="D644">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E644" t="s">
         <v>8</v>
@@ -15016,7 +15016,7 @@
         <v>7</v>
       </c>
       <c r="D645">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E645" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>7</v>
       </c>
       <c r="D646">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E646" t="s">
         <v>8</v>
@@ -15050,7 +15050,7 @@
         <v>7</v>
       </c>
       <c r="D647">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E647" t="s">
         <v>8</v>
@@ -15084,7 +15084,7 @@
         <v>7</v>
       </c>
       <c r="D649">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E649" t="s">
         <v>8</v>
@@ -15118,7 +15118,7 @@
         <v>7</v>
       </c>
       <c r="D651">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E651" t="s">
         <v>8</v>
@@ -15135,7 +15135,7 @@
         <v>7</v>
       </c>
       <c r="D652">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E652" t="s">
         <v>8</v>
@@ -15152,7 +15152,7 @@
         <v>7</v>
       </c>
       <c r="D653">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E653" t="s">
         <v>8</v>
@@ -15169,7 +15169,7 @@
         <v>7</v>
       </c>
       <c r="D654">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E654" t="s">
         <v>8</v>
@@ -15220,7 +15220,7 @@
         <v>7</v>
       </c>
       <c r="D657">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E657" t="s">
         <v>8</v>
@@ -15237,7 +15237,7 @@
         <v>7</v>
       </c>
       <c r="D658">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E658" t="s">
         <v>8</v>
@@ -15254,7 +15254,7 @@
         <v>7</v>
       </c>
       <c r="D659">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E659" t="s">
         <v>8</v>
@@ -15271,7 +15271,7 @@
         <v>7</v>
       </c>
       <c r="D660">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E660" t="s">
         <v>8</v>
@@ -15288,7 +15288,7 @@
         <v>7</v>
       </c>
       <c r="D661">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E661" t="s">
         <v>8</v>
@@ -15305,7 +15305,7 @@
         <v>7</v>
       </c>
       <c r="D662">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E662" t="s">
         <v>8</v>
@@ -15322,7 +15322,7 @@
         <v>7</v>
       </c>
       <c r="D663">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E663" t="s">
         <v>8</v>
@@ -15339,7 +15339,7 @@
         <v>7</v>
       </c>
       <c r="D664">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E664" t="s">
         <v>8</v>
@@ -15373,7 +15373,7 @@
         <v>7</v>
       </c>
       <c r="D666">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E666" t="s">
         <v>8</v>
@@ -15390,7 +15390,7 @@
         <v>7</v>
       </c>
       <c r="D667">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E667" t="s">
         <v>8</v>
@@ -15458,7 +15458,7 @@
         <v>7</v>
       </c>
       <c r="D671">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E671" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7</v>
       </c>
       <c r="D672">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E672" t="s">
         <v>8</v>
@@ -15492,7 +15492,7 @@
         <v>7</v>
       </c>
       <c r="D673">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E673" t="s">
         <v>8</v>
@@ -15509,7 +15509,7 @@
         <v>7</v>
       </c>
       <c r="D674">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E674" t="s">
         <v>8</v>
@@ -15543,7 +15543,7 @@
         <v>7</v>
       </c>
       <c r="D676">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E676" t="s">
         <v>8</v>
@@ -15560,7 +15560,7 @@
         <v>7</v>
       </c>
       <c r="D677">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E677" t="s">
         <v>8</v>
@@ -15577,7 +15577,7 @@
         <v>7</v>
       </c>
       <c r="D678">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E678" t="s">
         <v>8</v>
@@ -15594,7 +15594,7 @@
         <v>7</v>
       </c>
       <c r="D679">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E679" t="s">
         <v>8</v>
@@ -15611,7 +15611,7 @@
         <v>7</v>
       </c>
       <c r="D680">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E680" t="s">
         <v>8</v>
@@ -15679,7 +15679,7 @@
         <v>7</v>
       </c>
       <c r="D684">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E684" t="s">
         <v>8</v>
@@ -15713,7 +15713,7 @@
         <v>7</v>
       </c>
       <c r="D686">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E686" t="s">
         <v>8</v>
@@ -15747,7 +15747,7 @@
         <v>7</v>
       </c>
       <c r="D688">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E688" t="s">
         <v>8</v>
@@ -15781,7 +15781,7 @@
         <v>7</v>
       </c>
       <c r="D690">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E690" t="s">
         <v>8</v>
@@ -15798,7 +15798,7 @@
         <v>7</v>
       </c>
       <c r="D691">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E691" t="s">
         <v>8</v>
@@ -15815,7 +15815,7 @@
         <v>7</v>
       </c>
       <c r="D692">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E692" t="s">
         <v>8</v>
@@ -15832,7 +15832,7 @@
         <v>7</v>
       </c>
       <c r="D693">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E693" t="s">
         <v>8</v>
@@ -15849,7 +15849,7 @@
         <v>7</v>
       </c>
       <c r="D694">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E694" t="s">
         <v>8</v>
@@ -15866,7 +15866,7 @@
         <v>7</v>
       </c>
       <c r="D695">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E695" t="s">
         <v>8</v>
@@ -15883,7 +15883,7 @@
         <v>7</v>
       </c>
       <c r="D696">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E696" t="s">
         <v>8</v>
@@ -15900,7 +15900,7 @@
         <v>7</v>
       </c>
       <c r="D697">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E697" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>7</v>
       </c>
       <c r="D698">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E698" t="s">
         <v>8</v>
@@ -15934,7 +15934,7 @@
         <v>7</v>
       </c>
       <c r="D699">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E699" t="s">
         <v>8</v>
@@ -15951,7 +15951,7 @@
         <v>7</v>
       </c>
       <c r="D700">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E700" t="s">
         <v>8</v>
@@ -15968,7 +15968,7 @@
         <v>7</v>
       </c>
       <c r="D701">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E701" t="s">
         <v>8</v>
@@ -15985,7 +15985,7 @@
         <v>7</v>
       </c>
       <c r="D702">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E702" t="s">
         <v>8</v>
@@ -16002,7 +16002,7 @@
         <v>7</v>
       </c>
       <c r="D703">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E703" t="s">
         <v>8</v>
@@ -16019,7 +16019,7 @@
         <v>7</v>
       </c>
       <c r="D704">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E704" t="s">
         <v>8</v>
@@ -16036,7 +16036,7 @@
         <v>7</v>
       </c>
       <c r="D705">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E705" t="s">
         <v>8</v>
@@ -16053,7 +16053,7 @@
         <v>7</v>
       </c>
       <c r="D706">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E706" t="s">
         <v>8</v>
@@ -16070,7 +16070,7 @@
         <v>7</v>
       </c>
       <c r="D707">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E707" t="s">
         <v>8</v>
@@ -16087,7 +16087,7 @@
         <v>7</v>
       </c>
       <c r="D708">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E708" t="s">
         <v>8</v>
@@ -16104,7 +16104,7 @@
         <v>7</v>
       </c>
       <c r="D709">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E709" t="s">
         <v>8</v>
@@ -16121,7 +16121,7 @@
         <v>7</v>
       </c>
       <c r="D710">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E710" t="s">
         <v>8</v>
@@ -16138,7 +16138,7 @@
         <v>7</v>
       </c>
       <c r="D711">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E711" t="s">
         <v>8</v>
@@ -16155,7 +16155,7 @@
         <v>7</v>
       </c>
       <c r="D712">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E712" t="s">
         <v>8</v>
@@ -16172,7 +16172,7 @@
         <v>7</v>
       </c>
       <c r="D713">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E713" t="s">
         <v>8</v>
@@ -16189,7 +16189,7 @@
         <v>7</v>
       </c>
       <c r="D714">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E714" t="s">
         <v>8</v>
@@ -16206,7 +16206,7 @@
         <v>7</v>
       </c>
       <c r="D715">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E715" t="s">
         <v>8</v>
@@ -16223,7 +16223,7 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E716" t="s">
         <v>8</v>
@@ -16240,7 +16240,7 @@
         <v>7</v>
       </c>
       <c r="D717">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E717" t="s">
         <v>8</v>
@@ -16257,7 +16257,7 @@
         <v>7</v>
       </c>
       <c r="D718">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E718" t="s">
         <v>8</v>
@@ -16274,7 +16274,7 @@
         <v>7</v>
       </c>
       <c r="D719">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E719" t="s">
         <v>8</v>
@@ -16291,7 +16291,7 @@
         <v>7</v>
       </c>
       <c r="D720">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E720" t="s">
         <v>8</v>
@@ -16308,7 +16308,7 @@
         <v>7</v>
       </c>
       <c r="D721">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E721" t="s">
         <v>8</v>
@@ -16325,7 +16325,7 @@
         <v>7</v>
       </c>
       <c r="D722">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E722" t="s">
         <v>8</v>
@@ -16342,7 +16342,7 @@
         <v>7</v>
       </c>
       <c r="D723">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E723" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7</v>
       </c>
       <c r="D724">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E724" t="s">
         <v>8</v>
@@ -16376,7 +16376,7 @@
         <v>7</v>
       </c>
       <c r="D725">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E725" t="s">
         <v>8</v>
@@ -16393,7 +16393,7 @@
         <v>7</v>
       </c>
       <c r="D726">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E726" t="s">
         <v>8</v>
@@ -16410,7 +16410,7 @@
         <v>7</v>
       </c>
       <c r="D727">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E727" t="s">
         <v>8</v>
@@ -16427,7 +16427,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E728" t="s">
         <v>8</v>
@@ -16444,7 +16444,7 @@
         <v>7</v>
       </c>
       <c r="D729">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E729" t="s">
         <v>8</v>
@@ -16461,7 +16461,7 @@
         <v>7</v>
       </c>
       <c r="D730">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E730" t="s">
         <v>8</v>
@@ -16478,7 +16478,7 @@
         <v>7</v>
       </c>
       <c r="D731">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E731" t="s">
         <v>8</v>
@@ -16495,7 +16495,7 @@
         <v>7</v>
       </c>
       <c r="D732">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E732" t="s">
         <v>8</v>
@@ -16512,7 +16512,7 @@
         <v>7</v>
       </c>
       <c r="D733">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E733" t="s">
         <v>8</v>
@@ -16529,7 +16529,7 @@
         <v>7</v>
       </c>
       <c r="D734">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E734" t="s">
         <v>8</v>
@@ -16546,7 +16546,7 @@
         <v>7</v>
       </c>
       <c r="D735">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E735" t="s">
         <v>8</v>
@@ -16563,7 +16563,7 @@
         <v>7</v>
       </c>
       <c r="D736">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E736" t="s">
         <v>8</v>
@@ -16580,7 +16580,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E737" t="s">
         <v>8</v>
@@ -16597,7 +16597,7 @@
         <v>7</v>
       </c>
       <c r="D738">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E738" t="s">
         <v>8</v>
@@ -16614,7 +16614,7 @@
         <v>7</v>
       </c>
       <c r="D739">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E739" t="s">
         <v>8</v>
@@ -16631,7 +16631,7 @@
         <v>7</v>
       </c>
       <c r="D740">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E740" t="s">
         <v>8</v>
@@ -16648,7 +16648,7 @@
         <v>7</v>
       </c>
       <c r="D741">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E741" t="s">
         <v>8</v>
@@ -16665,7 +16665,7 @@
         <v>7</v>
       </c>
       <c r="D742">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E742" t="s">
         <v>8</v>
@@ -16682,7 +16682,7 @@
         <v>7</v>
       </c>
       <c r="D743">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E743" t="s">
         <v>8</v>
@@ -16699,7 +16699,7 @@
         <v>7</v>
       </c>
       <c r="D744">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E744" t="s">
         <v>8</v>
@@ -16716,7 +16716,7 @@
         <v>7</v>
       </c>
       <c r="D745">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E745" t="s">
         <v>8</v>
@@ -16733,7 +16733,7 @@
         <v>7</v>
       </c>
       <c r="D746">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E746" t="s">
         <v>8</v>
@@ -16750,7 +16750,7 @@
         <v>7</v>
       </c>
       <c r="D747">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E747" t="s">
         <v>8</v>
@@ -16767,7 +16767,7 @@
         <v>7</v>
       </c>
       <c r="D748">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E748" t="s">
         <v>8</v>
@@ -16784,7 +16784,7 @@
         <v>7</v>
       </c>
       <c r="D749">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E749" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>7</v>
       </c>
       <c r="D750">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E750" t="s">
         <v>8</v>
@@ -16818,7 +16818,7 @@
         <v>7</v>
       </c>
       <c r="D751">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E751" t="s">
         <v>8</v>
@@ -16835,7 +16835,7 @@
         <v>7</v>
       </c>
       <c r="D752">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E752" t="s">
         <v>8</v>
@@ -16852,7 +16852,7 @@
         <v>7</v>
       </c>
       <c r="D753">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E753" t="s">
         <v>8</v>
@@ -16869,7 +16869,7 @@
         <v>7</v>
       </c>
       <c r="D754">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E754" t="s">
         <v>8</v>
@@ -16886,7 +16886,7 @@
         <v>7</v>
       </c>
       <c r="D755">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E755" t="s">
         <v>8</v>
@@ -16903,7 +16903,7 @@
         <v>7</v>
       </c>
       <c r="D756">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E756" t="s">
         <v>8</v>
@@ -16920,7 +16920,7 @@
         <v>7</v>
       </c>
       <c r="D757">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E757" t="s">
         <v>8</v>
@@ -16937,7 +16937,7 @@
         <v>7</v>
       </c>
       <c r="D758">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E758" t="s">
         <v>8</v>
@@ -16954,7 +16954,7 @@
         <v>7</v>
       </c>
       <c r="D759">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E759" t="s">
         <v>8</v>
@@ -16971,7 +16971,7 @@
         <v>7</v>
       </c>
       <c r="D760">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E760" t="s">
         <v>8</v>
@@ -16988,7 +16988,7 @@
         <v>7</v>
       </c>
       <c r="D761">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E761" t="s">
         <v>8</v>
@@ -17005,7 +17005,7 @@
         <v>7</v>
       </c>
       <c r="D762">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E762" t="s">
         <v>8</v>
@@ -17022,7 +17022,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E763" t="s">
         <v>8</v>
@@ -17039,7 +17039,7 @@
         <v>7</v>
       </c>
       <c r="D764">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E764" t="s">
         <v>8</v>
@@ -17056,7 +17056,7 @@
         <v>7</v>
       </c>
       <c r="D765">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E765" t="s">
         <v>8</v>
@@ -17073,7 +17073,7 @@
         <v>7</v>
       </c>
       <c r="D766">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E766" t="s">
         <v>8</v>
@@ -17090,7 +17090,7 @@
         <v>7</v>
       </c>
       <c r="D767">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E767" t="s">
         <v>8</v>
@@ -17107,7 +17107,7 @@
         <v>7</v>
       </c>
       <c r="D768">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E768" t="s">
         <v>8</v>
@@ -17124,7 +17124,7 @@
         <v>7</v>
       </c>
       <c r="D769">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E769" t="s">
         <v>8</v>
@@ -17141,7 +17141,7 @@
         <v>7</v>
       </c>
       <c r="D770">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E770" t="s">
         <v>8</v>
@@ -17158,7 +17158,7 @@
         <v>7</v>
       </c>
       <c r="D771">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E771" t="s">
         <v>8</v>
@@ -17175,7 +17175,7 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E772" t="s">
         <v>8</v>
@@ -17192,7 +17192,7 @@
         <v>7</v>
       </c>
       <c r="D773">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E773" t="s">
         <v>8</v>
@@ -17209,7 +17209,7 @@
         <v>7</v>
       </c>
       <c r="D774">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E774" t="s">
         <v>8</v>
@@ -17226,7 +17226,7 @@
         <v>7</v>
       </c>
       <c r="D775">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E775" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>7</v>
       </c>
       <c r="D776">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E776" t="s">
         <v>8</v>
@@ -17260,7 +17260,7 @@
         <v>7</v>
       </c>
       <c r="D777">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E777" t="s">
         <v>8</v>
@@ -17277,7 +17277,7 @@
         <v>7</v>
       </c>
       <c r="D778">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E778" t="s">
         <v>8</v>
@@ -17294,7 +17294,7 @@
         <v>7</v>
       </c>
       <c r="D779">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E779" t="s">
         <v>8</v>
@@ -17311,7 +17311,7 @@
         <v>7</v>
       </c>
       <c r="D780">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E780" t="s">
         <v>8</v>
@@ -17328,7 +17328,7 @@
         <v>7</v>
       </c>
       <c r="D781">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E781" t="s">
         <v>8</v>
@@ -17345,7 +17345,7 @@
         <v>7</v>
       </c>
       <c r="D782">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E782" t="s">
         <v>8</v>
@@ -17362,7 +17362,7 @@
         <v>7</v>
       </c>
       <c r="D783">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E783" t="s">
         <v>8</v>
@@ -17379,7 +17379,7 @@
         <v>7</v>
       </c>
       <c r="D784">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E784" t="s">
         <v>8</v>
@@ -17396,7 +17396,7 @@
         <v>7</v>
       </c>
       <c r="D785">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E785" t="s">
         <v>8</v>
@@ -17413,7 +17413,7 @@
         <v>7</v>
       </c>
       <c r="D786">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E786" t="s">
         <v>8</v>
@@ -17430,7 +17430,7 @@
         <v>7</v>
       </c>
       <c r="D787">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E787" t="s">
         <v>8</v>
@@ -17447,7 +17447,7 @@
         <v>7</v>
       </c>
       <c r="D788">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E788" t="s">
         <v>8</v>
@@ -17464,7 +17464,7 @@
         <v>7</v>
       </c>
       <c r="D789">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="E789" t="s">
         <v>8</v>
@@ -17481,7 +17481,7 @@
         <v>7</v>
       </c>
       <c r="D790">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E790" t="s">
         <v>8</v>
@@ -17498,7 +17498,7 @@
         <v>7</v>
       </c>
       <c r="D791">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E791" t="s">
         <v>8</v>
@@ -17515,7 +17515,7 @@
         <v>7</v>
       </c>
       <c r="D792">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E792" t="s">
         <v>8</v>
@@ -17532,7 +17532,7 @@
         <v>7</v>
       </c>
       <c r="D793">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E793" t="s">
         <v>8</v>
@@ -17549,7 +17549,7 @@
         <v>7</v>
       </c>
       <c r="D794">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E794" t="s">
         <v>8</v>
@@ -17566,7 +17566,7 @@
         <v>7</v>
       </c>
       <c r="D795">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E795" t="s">
         <v>8</v>
@@ -17583,7 +17583,7 @@
         <v>7</v>
       </c>
       <c r="D796">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E796" t="s">
         <v>8</v>
@@ -17600,7 +17600,7 @@
         <v>7</v>
       </c>
       <c r="D797">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E797" t="s">
         <v>8</v>
@@ -17617,7 +17617,7 @@
         <v>7</v>
       </c>
       <c r="D798">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E798" t="s">
         <v>8</v>
@@ -17634,7 +17634,7 @@
         <v>7</v>
       </c>
       <c r="D799">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E799" t="s">
         <v>8</v>
@@ -17651,7 +17651,7 @@
         <v>7</v>
       </c>
       <c r="D800">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E800" t="s">
         <v>8</v>
@@ -17668,7 +17668,7 @@
         <v>7</v>
       </c>
       <c r="D801">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E801" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>7</v>
       </c>
       <c r="D802">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E802" t="s">
         <v>8</v>
@@ -17702,7 +17702,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E803" t="s">
         <v>8</v>
@@ -17719,7 +17719,7 @@
         <v>7</v>
       </c>
       <c r="D804">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E804" t="s">
         <v>8</v>
@@ -17736,7 +17736,7 @@
         <v>7</v>
       </c>
       <c r="D805">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E805" t="s">
         <v>8</v>
@@ -17753,7 +17753,7 @@
         <v>7</v>
       </c>
       <c r="D806">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E806" t="s">
         <v>8</v>
@@ -17770,7 +17770,7 @@
         <v>7</v>
       </c>
       <c r="D807">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E807" t="s">
         <v>8</v>
@@ -17787,7 +17787,7 @@
         <v>7</v>
       </c>
       <c r="D808">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E808" t="s">
         <v>8</v>
@@ -17804,7 +17804,7 @@
         <v>7</v>
       </c>
       <c r="D809">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E809" t="s">
         <v>8</v>
@@ -17821,7 +17821,7 @@
         <v>7</v>
       </c>
       <c r="D810">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E810" t="s">
         <v>8</v>
@@ -17838,7 +17838,7 @@
         <v>7</v>
       </c>
       <c r="D811">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E811" t="s">
         <v>8</v>
@@ -17855,7 +17855,7 @@
         <v>7</v>
       </c>
       <c r="D812">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E812" t="s">
         <v>8</v>
@@ -17872,7 +17872,7 @@
         <v>7</v>
       </c>
       <c r="D813">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E813" t="s">
         <v>8</v>
@@ -17889,7 +17889,7 @@
         <v>7</v>
       </c>
       <c r="D814">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E814" t="s">
         <v>8</v>
@@ -17906,7 +17906,7 @@
         <v>7</v>
       </c>
       <c r="D815">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E815" t="s">
         <v>8</v>
@@ -17923,7 +17923,7 @@
         <v>7</v>
       </c>
       <c r="D816">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E816" t="s">
         <v>8</v>
@@ -17940,7 +17940,7 @@
         <v>7</v>
       </c>
       <c r="D817">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E817" t="s">
         <v>8</v>
@@ -17957,7 +17957,7 @@
         <v>7</v>
       </c>
       <c r="D818">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E818" t="s">
         <v>8</v>
@@ -17974,7 +17974,7 @@
         <v>7</v>
       </c>
       <c r="D819">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E819" t="s">
         <v>8</v>
@@ -17991,7 +17991,7 @@
         <v>7</v>
       </c>
       <c r="D820">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E820" t="s">
         <v>8</v>
@@ -18008,7 +18008,7 @@
         <v>7</v>
       </c>
       <c r="D821">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E821" t="s">
         <v>8</v>
@@ -18025,7 +18025,7 @@
         <v>7</v>
       </c>
       <c r="D822">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E822" t="s">
         <v>8</v>
@@ -18042,7 +18042,7 @@
         <v>7</v>
       </c>
       <c r="D823">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E823" t="s">
         <v>8</v>
@@ -18059,7 +18059,7 @@
         <v>7</v>
       </c>
       <c r="D824">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E824" t="s">
         <v>8</v>
@@ -18076,7 +18076,7 @@
         <v>7</v>
       </c>
       <c r="D825">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E825" t="s">
         <v>8</v>
@@ -18093,7 +18093,7 @@
         <v>7</v>
       </c>
       <c r="D826">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E826" t="s">
         <v>8</v>
@@ -18110,7 +18110,7 @@
         <v>7</v>
       </c>
       <c r="D827">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E827" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E828" t="s">
         <v>8</v>
@@ -18144,7 +18144,7 @@
         <v>7</v>
       </c>
       <c r="D829">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E829" t="s">
         <v>8</v>
@@ -18161,7 +18161,7 @@
         <v>7</v>
       </c>
       <c r="D830">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E830" t="s">
         <v>8</v>
@@ -18178,7 +18178,7 @@
         <v>7</v>
       </c>
       <c r="D831">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E831" t="s">
         <v>8</v>
@@ -18195,7 +18195,7 @@
         <v>7</v>
       </c>
       <c r="D832">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E832" t="s">
         <v>8</v>
@@ -18212,7 +18212,7 @@
         <v>7</v>
       </c>
       <c r="D833">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="E833" t="s">
         <v>8</v>
@@ -18229,7 +18229,7 @@
         <v>7</v>
       </c>
       <c r="D834">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="E834" t="s">
         <v>8</v>
@@ -18246,7 +18246,7 @@
         <v>7</v>
       </c>
       <c r="D835">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E835" t="s">
         <v>8</v>
@@ -18263,7 +18263,7 @@
         <v>7</v>
       </c>
       <c r="D836">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E836" t="s">
         <v>8</v>
@@ -18280,7 +18280,7 @@
         <v>7</v>
       </c>
       <c r="D837">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="E837" t="s">
         <v>8</v>
@@ -18297,7 +18297,7 @@
         <v>7</v>
       </c>
       <c r="D838">
-        <v>7</v>
+        <v>102</v>
       </c>
       <c r="E838" t="s">
         <v>8</v>
@@ -18314,7 +18314,7 @@
         <v>7</v>
       </c>
       <c r="D839">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="E839" t="s">
         <v>8</v>
@@ -18331,7 +18331,7 @@
         <v>7</v>
       </c>
       <c r="D840">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E840" t="s">
         <v>8</v>
@@ -18348,7 +18348,7 @@
         <v>7</v>
       </c>
       <c r="D841">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="E841" t="s">
         <v>8</v>
@@ -18365,7 +18365,7 @@
         <v>7</v>
       </c>
       <c r="D842">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="E842" t="s">
         <v>8</v>
@@ -18382,7 +18382,7 @@
         <v>7</v>
       </c>
       <c r="D843">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="E843" t="s">
         <v>8</v>
@@ -18399,7 +18399,7 @@
         <v>7</v>
       </c>
       <c r="D844">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="E844" t="s">
         <v>8</v>
@@ -18416,7 +18416,7 @@
         <v>7</v>
       </c>
       <c r="D845">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="E845" t="s">
         <v>8</v>
@@ -18433,7 +18433,7 @@
         <v>7</v>
       </c>
       <c r="D846">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="E846" t="s">
         <v>8</v>
@@ -18450,7 +18450,7 @@
         <v>7</v>
       </c>
       <c r="D847">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="E847" t="s">
         <v>8</v>
@@ -18467,7 +18467,7 @@
         <v>7</v>
       </c>
       <c r="D848">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="E848" t="s">
         <v>8</v>
@@ -18484,7 +18484,7 @@
         <v>7</v>
       </c>
       <c r="D849">
-        <v>6</v>
+        <v>122</v>
       </c>
       <c r="E849" t="s">
         <v>8</v>
@@ -18501,7 +18501,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>6</v>
+        <v>173</v>
       </c>
       <c r="E850" t="s">
         <v>8</v>
@@ -18518,7 +18518,7 @@
         <v>7</v>
       </c>
       <c r="D851">
-        <v>7</v>
+        <v>125</v>
       </c>
       <c r="E851" t="s">
         <v>8</v>
@@ -18535,7 +18535,7 @@
         <v>7</v>
       </c>
       <c r="D852">
-        <v>7</v>
+        <v>165</v>
       </c>
       <c r="E852" t="s">
         <v>8</v>
@@ -18552,7 +18552,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>7</v>
+        <v>145</v>
       </c>
       <c r="E853" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>7</v>
       </c>
       <c r="D854">
-        <v>6</v>
+        <v>127</v>
       </c>
       <c r="E854" t="s">
         <v>8</v>
@@ -18586,7 +18586,7 @@
         <v>7</v>
       </c>
       <c r="D855">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="E855" t="s">
         <v>8</v>
@@ -18603,7 +18603,7 @@
         <v>7</v>
       </c>
       <c r="D856">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="E856" t="s">
         <v>8</v>
@@ -18620,7 +18620,7 @@
         <v>7</v>
       </c>
       <c r="D857">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="E857" t="s">
         <v>8</v>
@@ -18637,7 +18637,7 @@
         <v>7</v>
       </c>
       <c r="D858">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="E858" t="s">
         <v>8</v>
@@ -18654,7 +18654,7 @@
         <v>7</v>
       </c>
       <c r="D859">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="E859" t="s">
         <v>8</v>
@@ -18671,7 +18671,7 @@
         <v>7</v>
       </c>
       <c r="D860">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="E860" t="s">
         <v>8</v>
@@ -18688,7 +18688,7 @@
         <v>7</v>
       </c>
       <c r="D861">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="E861" t="s">
         <v>8</v>
@@ -18705,7 +18705,7 @@
         <v>7</v>
       </c>
       <c r="D862">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E862" t="s">
         <v>8</v>
@@ -18722,7 +18722,7 @@
         <v>7</v>
       </c>
       <c r="D863">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E863" t="s">
         <v>8</v>
@@ -18739,7 +18739,7 @@
         <v>7</v>
       </c>
       <c r="D864">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E864" t="s">
         <v>8</v>
@@ -18756,7 +18756,7 @@
         <v>7</v>
       </c>
       <c r="D865">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E865" t="s">
         <v>8</v>
@@ -18773,7 +18773,7 @@
         <v>7</v>
       </c>
       <c r="D866">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E866" t="s">
         <v>8</v>
@@ -18790,7 +18790,7 @@
         <v>7</v>
       </c>
       <c r="D867">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E867" t="s">
         <v>8</v>
@@ -18807,7 +18807,7 @@
         <v>7</v>
       </c>
       <c r="D868">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="E868" t="s">
         <v>8</v>
@@ -18824,7 +18824,7 @@
         <v>7</v>
       </c>
       <c r="D869">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="E869" t="s">
         <v>8</v>
@@ -18841,7 +18841,7 @@
         <v>7</v>
       </c>
       <c r="D870">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E870" t="s">
         <v>8</v>
@@ -18858,7 +18858,7 @@
         <v>7</v>
       </c>
       <c r="D871">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E871" t="s">
         <v>8</v>
@@ -18875,7 +18875,7 @@
         <v>7</v>
       </c>
       <c r="D872">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E872" t="s">
         <v>8</v>
@@ -18892,7 +18892,7 @@
         <v>7</v>
       </c>
       <c r="D873">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E873" t="s">
         <v>8</v>
@@ -18909,7 +18909,7 @@
         <v>7</v>
       </c>
       <c r="D874">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E874" t="s">
         <v>8</v>
@@ -18926,7 +18926,7 @@
         <v>7</v>
       </c>
       <c r="D875">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E875" t="s">
         <v>8</v>
@@ -18943,7 +18943,7 @@
         <v>7</v>
       </c>
       <c r="D876">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E876" t="s">
         <v>8</v>
@@ -18960,7 +18960,7 @@
         <v>7</v>
       </c>
       <c r="D877">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E877" t="s">
         <v>8</v>
@@ -18977,7 +18977,7 @@
         <v>7</v>
       </c>
       <c r="D878">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E878" t="s">
         <v>8</v>
@@ -18994,7 +18994,7 @@
         <v>7</v>
       </c>
       <c r="D879">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E879" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>7</v>
       </c>
       <c r="D880">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E880" t="s">
         <v>8</v>
@@ -19028,7 +19028,7 @@
         <v>7</v>
       </c>
       <c r="D881">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E881" t="s">
         <v>8</v>
@@ -19062,7 +19062,7 @@
         <v>7</v>
       </c>
       <c r="D883">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E883" t="s">
         <v>8</v>
@@ -19079,7 +19079,7 @@
         <v>7</v>
       </c>
       <c r="D884">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E884" t="s">
         <v>8</v>
@@ -19096,7 +19096,7 @@
         <v>7</v>
       </c>
       <c r="D885">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E885" t="s">
         <v>8</v>
@@ -19113,7 +19113,7 @@
         <v>7</v>
       </c>
       <c r="D886">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E886" t="s">
         <v>8</v>
@@ -19130,7 +19130,7 @@
         <v>7</v>
       </c>
       <c r="D887">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E887" t="s">
         <v>8</v>
@@ -19181,7 +19181,7 @@
         <v>7</v>
       </c>
       <c r="D890">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E890" t="s">
         <v>8</v>
@@ -19198,7 +19198,7 @@
         <v>7</v>
       </c>
       <c r="D891">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E891" t="s">
         <v>8</v>
@@ -19232,7 +19232,7 @@
         <v>7</v>
       </c>
       <c r="D893">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E893" t="s">
         <v>8</v>
@@ -19266,7 +19266,7 @@
         <v>7</v>
       </c>
       <c r="D895">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E895" t="s">
         <v>8</v>
@@ -19283,7 +19283,7 @@
         <v>7</v>
       </c>
       <c r="D896">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E896" t="s">
         <v>8</v>
@@ -19300,7 +19300,7 @@
         <v>7</v>
       </c>
       <c r="D897">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E897" t="s">
         <v>8</v>
@@ -19317,7 +19317,7 @@
         <v>7</v>
       </c>
       <c r="D898">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E898" t="s">
         <v>8</v>
@@ -19351,7 +19351,7 @@
         <v>7</v>
       </c>
       <c r="D900">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E900" t="s">
         <v>8</v>
@@ -19368,7 +19368,7 @@
         <v>7</v>
       </c>
       <c r="D901">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E901" t="s">
         <v>8</v>
@@ -19385,7 +19385,7 @@
         <v>7</v>
       </c>
       <c r="D902">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E902" t="s">
         <v>8</v>
@@ -19402,7 +19402,7 @@
         <v>7</v>
       </c>
       <c r="D903">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E903" t="s">
         <v>8</v>
@@ -19419,7 +19419,7 @@
         <v>7</v>
       </c>
       <c r="D904">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E904" t="s">
         <v>8</v>
@@ -19436,7 +19436,7 @@
         <v>7</v>
       </c>
       <c r="D905">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E905" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>7</v>
       </c>
       <c r="D906">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E906" t="s">
         <v>8</v>
@@ -19470,7 +19470,7 @@
         <v>7</v>
       </c>
       <c r="D907">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E907" t="s">
         <v>8</v>
@@ -19487,7 +19487,7 @@
         <v>7</v>
       </c>
       <c r="D908">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E908" t="s">
         <v>8</v>
@@ -19504,7 +19504,7 @@
         <v>7</v>
       </c>
       <c r="D909">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E909" t="s">
         <v>8</v>
@@ -19521,7 +19521,7 @@
         <v>7</v>
       </c>
       <c r="D910">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E910" t="s">
         <v>8</v>
@@ -19538,7 +19538,7 @@
         <v>7</v>
       </c>
       <c r="D911">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E911" t="s">
         <v>8</v>
@@ -19572,7 +19572,7 @@
         <v>7</v>
       </c>
       <c r="D913">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E913" t="s">
         <v>8</v>
@@ -19589,7 +19589,7 @@
         <v>7</v>
       </c>
       <c r="D914">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E914" t="s">
         <v>8</v>
@@ -19606,7 +19606,7 @@
         <v>7</v>
       </c>
       <c r="D915">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E915" t="s">
         <v>8</v>
@@ -19623,7 +19623,7 @@
         <v>7</v>
       </c>
       <c r="D916">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E916" t="s">
         <v>8</v>
@@ -19640,7 +19640,7 @@
         <v>7</v>
       </c>
       <c r="D917">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E917" t="s">
         <v>8</v>
@@ -19674,7 +19674,7 @@
         <v>7</v>
       </c>
       <c r="D919">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E919" t="s">
         <v>8</v>
@@ -19691,7 +19691,7 @@
         <v>7</v>
       </c>
       <c r="D920">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E920" t="s">
         <v>8</v>
@@ -19708,7 +19708,7 @@
         <v>7</v>
       </c>
       <c r="D921">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E921" t="s">
         <v>8</v>
@@ -19725,7 +19725,7 @@
         <v>7</v>
       </c>
       <c r="D922">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E922" t="s">
         <v>8</v>
@@ -19742,7 +19742,7 @@
         <v>7</v>
       </c>
       <c r="D923">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E923" t="s">
         <v>8</v>
@@ -19759,7 +19759,7 @@
         <v>7</v>
       </c>
       <c r="D924">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E924" t="s">
         <v>8</v>
@@ -19776,7 +19776,7 @@
         <v>7</v>
       </c>
       <c r="D925">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E925" t="s">
         <v>8</v>
@@ -19793,7 +19793,7 @@
         <v>7</v>
       </c>
       <c r="D926">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E926" t="s">
         <v>8</v>
@@ -19810,7 +19810,7 @@
         <v>7</v>
       </c>
       <c r="D927">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E927" t="s">
         <v>8</v>
@@ -19827,7 +19827,7 @@
         <v>7</v>
       </c>
       <c r="D928">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E928" t="s">
         <v>8</v>
@@ -19861,7 +19861,7 @@
         <v>7</v>
       </c>
       <c r="D930">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E930" t="s">
         <v>8</v>
@@ -19878,7 +19878,7 @@
         <v>7</v>
       </c>
       <c r="D931">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E931" t="s">
         <v>8</v>
@@ -19912,7 +19912,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E933" t="s">
         <v>8</v>
@@ -19997,7 +19997,7 @@
         <v>7</v>
       </c>
       <c r="D938">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E938" t="s">
         <v>8</v>
@@ -20014,7 +20014,7 @@
         <v>7</v>
       </c>
       <c r="D939">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E939" t="s">
         <v>8</v>
@@ -20031,7 +20031,7 @@
         <v>7</v>
       </c>
       <c r="D940">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E940" t="s">
         <v>8</v>
@@ -20048,7 +20048,7 @@
         <v>7</v>
       </c>
       <c r="D941">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E941" t="s">
         <v>8</v>
@@ -20116,7 +20116,7 @@
         <v>7</v>
       </c>
       <c r="D945">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E945" t="s">
         <v>8</v>
@@ -20133,7 +20133,7 @@
         <v>7</v>
       </c>
       <c r="D946">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E946" t="s">
         <v>8</v>
@@ -20150,7 +20150,7 @@
         <v>7</v>
       </c>
       <c r="D947">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E947" t="s">
         <v>8</v>
@@ -20167,7 +20167,7 @@
         <v>7</v>
       </c>
       <c r="D948">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E948" t="s">
         <v>8</v>
@@ -20201,7 +20201,7 @@
         <v>7</v>
       </c>
       <c r="D950">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E950" t="s">
         <v>8</v>
@@ -20218,7 +20218,7 @@
         <v>7</v>
       </c>
       <c r="D951">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E951" t="s">
         <v>8</v>
@@ -20235,7 +20235,7 @@
         <v>7</v>
       </c>
       <c r="D952">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E952" t="s">
         <v>8</v>
@@ -20252,7 +20252,7 @@
         <v>7</v>
       </c>
       <c r="D953">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E953" t="s">
         <v>8</v>
@@ -20269,7 +20269,7 @@
         <v>7</v>
       </c>
       <c r="D954">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E954" t="s">
         <v>8</v>
@@ -20286,7 +20286,7 @@
         <v>7</v>
       </c>
       <c r="D955">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E955" t="s">
         <v>8</v>
@@ -20303,7 +20303,7 @@
         <v>7</v>
       </c>
       <c r="D956">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E956" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>7</v>
       </c>
       <c r="D958">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E958" t="s">
         <v>8</v>
@@ -20354,7 +20354,7 @@
         <v>7</v>
       </c>
       <c r="D959">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E959" t="s">
         <v>8</v>
@@ -20371,7 +20371,7 @@
         <v>7</v>
       </c>
       <c r="D960">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E960" t="s">
         <v>8</v>
@@ -20388,7 +20388,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E961" t="s">
         <v>8</v>
@@ -20422,7 +20422,7 @@
         <v>7</v>
       </c>
       <c r="D963">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E963" t="s">
         <v>8</v>
@@ -20456,7 +20456,7 @@
         <v>7</v>
       </c>
       <c r="D965">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E965" t="s">
         <v>8</v>
@@ -20473,7 +20473,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E966" t="s">
         <v>8</v>
@@ -20490,7 +20490,7 @@
         <v>7</v>
       </c>
       <c r="D967">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E967" t="s">
         <v>8</v>
@@ -20524,7 +20524,7 @@
         <v>7</v>
       </c>
       <c r="D969">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E969" t="s">
         <v>8</v>
@@ -20541,7 +20541,7 @@
         <v>7</v>
       </c>
       <c r="D970">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E970" t="s">
         <v>8</v>
@@ -20558,7 +20558,7 @@
         <v>7</v>
       </c>
       <c r="D971">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E971" t="s">
         <v>8</v>
@@ -20575,7 +20575,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E972" t="s">
         <v>8</v>
@@ -20592,7 +20592,7 @@
         <v>7</v>
       </c>
       <c r="D973">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E973" t="s">
         <v>8</v>
@@ -20626,7 +20626,7 @@
         <v>7</v>
       </c>
       <c r="D975">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E975" t="s">
         <v>8</v>
@@ -20643,7 +20643,7 @@
         <v>7</v>
       </c>
       <c r="D976">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E976" t="s">
         <v>8</v>
@@ -20660,7 +20660,7 @@
         <v>7</v>
       </c>
       <c r="D977">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E977" t="s">
         <v>8</v>
@@ -20694,7 +20694,7 @@
         <v>7</v>
       </c>
       <c r="D979">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E979" t="s">
         <v>8</v>
@@ -20711,7 +20711,7 @@
         <v>7</v>
       </c>
       <c r="D980">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E980" t="s">
         <v>8</v>
@@ -20728,7 +20728,7 @@
         <v>7</v>
       </c>
       <c r="D981">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E981" t="s">
         <v>8</v>
@@ -20745,7 +20745,7 @@
         <v>7</v>
       </c>
       <c r="D982">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E982" t="s">
         <v>8</v>
@@ -20762,7 +20762,7 @@
         <v>7</v>
       </c>
       <c r="D983">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E983" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E984" t="s">
         <v>8</v>
@@ -20796,7 +20796,7 @@
         <v>7</v>
       </c>
       <c r="D985">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E985" t="s">
         <v>8</v>
@@ -20830,7 +20830,7 @@
         <v>7</v>
       </c>
       <c r="D987">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E987" t="s">
         <v>8</v>
@@ -20864,7 +20864,7 @@
         <v>7</v>
       </c>
       <c r="D989">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E989" t="s">
         <v>8</v>
@@ -20898,7 +20898,7 @@
         <v>7</v>
       </c>
       <c r="D991">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E991" t="s">
         <v>8</v>
@@ -20915,7 +20915,7 @@
         <v>7</v>
       </c>
       <c r="D992">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E992" t="s">
         <v>8</v>
@@ -20932,7 +20932,7 @@
         <v>7</v>
       </c>
       <c r="D993">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E993" t="s">
         <v>8</v>
@@ -20983,7 +20983,7 @@
         <v>7</v>
       </c>
       <c r="D996">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E996" t="s">
         <v>8</v>
@@ -21000,7 +21000,7 @@
         <v>7</v>
       </c>
       <c r="D997">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E997" t="s">
         <v>8</v>
@@ -21017,7 +21017,7 @@
         <v>7</v>
       </c>
       <c r="D998">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E998" t="s">
         <v>8</v>
@@ -21051,7 +21051,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1000" t="s">
         <v>8</v>
@@ -21068,7 +21068,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1001" t="s">
         <v>8</v>
@@ -21085,7 +21085,7 @@
         <v>7</v>
       </c>
       <c r="D1002">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1002" t="s">
         <v>8</v>
@@ -21102,7 +21102,7 @@
         <v>7</v>
       </c>
       <c r="D1003">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E1003" t="s">
         <v>8</v>
@@ -21119,7 +21119,7 @@
         <v>7</v>
       </c>
       <c r="D1004">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1004" t="s">
         <v>8</v>
@@ -21136,7 +21136,7 @@
         <v>7</v>
       </c>
       <c r="D1005">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1005" t="s">
         <v>8</v>
@@ -21153,7 +21153,7 @@
         <v>7</v>
       </c>
       <c r="D1006">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1006" t="s">
         <v>8</v>
@@ -21170,7 +21170,7 @@
         <v>7</v>
       </c>
       <c r="D1007">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1007" t="s">
         <v>8</v>
@@ -21204,7 +21204,7 @@
         <v>7</v>
       </c>
       <c r="D1009">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1009" t="s">
         <v>8</v>
@@ -21255,7 +21255,7 @@
         <v>7</v>
       </c>
       <c r="D1012">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1012" t="s">
         <v>8</v>
@@ -21272,7 +21272,7 @@
         <v>7</v>
       </c>
       <c r="D1013">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1013" t="s">
         <v>8</v>
@@ -21306,7 +21306,7 @@
         <v>7</v>
       </c>
       <c r="D1015">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1015" t="s">
         <v>8</v>
@@ -21340,7 +21340,7 @@
         <v>7</v>
       </c>
       <c r="D1017">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1017" t="s">
         <v>8</v>
@@ -21374,7 +21374,7 @@
         <v>7</v>
       </c>
       <c r="D1019">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1019" t="s">
         <v>8</v>
@@ -21408,7 +21408,7 @@
         <v>7</v>
       </c>
       <c r="D1021">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1021" t="s">
         <v>8</v>
@@ -21425,7 +21425,7 @@
         <v>7</v>
       </c>
       <c r="D1022">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1022" t="s">
         <v>8</v>
@@ -21459,7 +21459,7 @@
         <v>7</v>
       </c>
       <c r="D1024">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1024" t="s">
         <v>8</v>
@@ -21476,7 +21476,7 @@
         <v>7</v>
       </c>
       <c r="D1025">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1025" t="s">
         <v>8</v>
@@ -21493,7 +21493,7 @@
         <v>7</v>
       </c>
       <c r="D1026">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1026" t="s">
         <v>8</v>
@@ -21527,7 +21527,7 @@
         <v>7</v>
       </c>
       <c r="D1028">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1028" t="s">
         <v>8</v>
@@ -21544,7 +21544,7 @@
         <v>7</v>
       </c>
       <c r="D1029">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1029" t="s">
         <v>8</v>
@@ -21561,7 +21561,7 @@
         <v>7</v>
       </c>
       <c r="D1030">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1030" t="s">
         <v>8</v>
@@ -21578,7 +21578,7 @@
         <v>7</v>
       </c>
       <c r="D1031">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1031" t="s">
         <v>8</v>
@@ -21595,7 +21595,7 @@
         <v>7</v>
       </c>
       <c r="D1032">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1032" t="s">
         <v>8</v>
@@ -21612,7 +21612,7 @@
         <v>7</v>
       </c>
       <c r="D1033">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1033" t="s">
         <v>8</v>
@@ -21629,7 +21629,7 @@
         <v>7</v>
       </c>
       <c r="D1034">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1034" t="s">
         <v>8</v>
@@ -21646,7 +21646,7 @@
         <v>7</v>
       </c>
       <c r="D1035">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1035" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>7</v>
       </c>
       <c r="D1036">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1036" t="s">
         <v>8</v>
@@ -21680,7 +21680,7 @@
         <v>7</v>
       </c>
       <c r="D1037">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1037" t="s">
         <v>8</v>
@@ -21714,7 +21714,7 @@
         <v>7</v>
       </c>
       <c r="D1039">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1039" t="s">
         <v>8</v>
@@ -21731,7 +21731,7 @@
         <v>7</v>
       </c>
       <c r="D1040">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1040" t="s">
         <v>8</v>
@@ -21765,7 +21765,7 @@
         <v>7</v>
       </c>
       <c r="D1042">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1042" t="s">
         <v>8</v>
@@ -21782,7 +21782,7 @@
         <v>7</v>
       </c>
       <c r="D1043">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1043" t="s">
         <v>8</v>
@@ -21799,7 +21799,7 @@
         <v>7</v>
       </c>
       <c r="D1044">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1044" t="s">
         <v>8</v>
@@ -21833,7 +21833,7 @@
         <v>7</v>
       </c>
       <c r="D1046">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1046" t="s">
         <v>8</v>
@@ -21867,7 +21867,7 @@
         <v>7</v>
       </c>
       <c r="D1048">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1048" t="s">
         <v>8</v>
@@ -21884,7 +21884,7 @@
         <v>7</v>
       </c>
       <c r="D1049">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1049" t="s">
         <v>8</v>
@@ -21901,7 +21901,7 @@
         <v>7</v>
       </c>
       <c r="D1050">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1050" t="s">
         <v>8</v>
@@ -21935,7 +21935,7 @@
         <v>7</v>
       </c>
       <c r="D1052">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1052" t="s">
         <v>8</v>
@@ -21969,7 +21969,7 @@
         <v>7</v>
       </c>
       <c r="D1054">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1054" t="s">
         <v>8</v>
@@ -21986,7 +21986,7 @@
         <v>7</v>
       </c>
       <c r="D1055">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1055" t="s">
         <v>8</v>
@@ -22003,7 +22003,7 @@
         <v>7</v>
       </c>
       <c r="D1056">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1056" t="s">
         <v>8</v>
@@ -22020,7 +22020,7 @@
         <v>7</v>
       </c>
       <c r="D1057">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1057" t="s">
         <v>8</v>
@@ -22054,7 +22054,7 @@
         <v>7</v>
       </c>
       <c r="D1059">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1059" t="s">
         <v>8</v>
@@ -22071,7 +22071,7 @@
         <v>7</v>
       </c>
       <c r="D1060">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1060" t="s">
         <v>8</v>
@@ -22088,7 +22088,7 @@
         <v>7</v>
       </c>
       <c r="D1061">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1061" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>7</v>
       </c>
       <c r="D1062">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1062" t="s">
         <v>8</v>
@@ -22122,7 +22122,7 @@
         <v>7</v>
       </c>
       <c r="D1063">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1063" t="s">
         <v>8</v>
@@ -22156,7 +22156,7 @@
         <v>7</v>
       </c>
       <c r="D1065">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1065" t="s">
         <v>8</v>
@@ -22173,7 +22173,7 @@
         <v>7</v>
       </c>
       <c r="D1066">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1066" t="s">
         <v>8</v>
@@ -22190,7 +22190,7 @@
         <v>7</v>
       </c>
       <c r="D1067">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1067" t="s">
         <v>8</v>
@@ -22224,7 +22224,7 @@
         <v>7</v>
       </c>
       <c r="D1069">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1069" t="s">
         <v>8</v>
@@ -22241,7 +22241,7 @@
         <v>7</v>
       </c>
       <c r="D1070">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1070" t="s">
         <v>8</v>
@@ -22258,7 +22258,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1071" t="s">
         <v>8</v>
@@ -22275,7 +22275,7 @@
         <v>7</v>
       </c>
       <c r="D1072">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1072" t="s">
         <v>8</v>
@@ -22292,7 +22292,7 @@
         <v>7</v>
       </c>
       <c r="D1073">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1073" t="s">
         <v>8</v>
@@ -22309,7 +22309,7 @@
         <v>7</v>
       </c>
       <c r="D1074">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1074" t="s">
         <v>8</v>
@@ -22326,7 +22326,7 @@
         <v>7</v>
       </c>
       <c r="D1075">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1075" t="s">
         <v>8</v>
@@ -22343,7 +22343,7 @@
         <v>7</v>
       </c>
       <c r="D1076">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1076" t="s">
         <v>8</v>
@@ -22360,7 +22360,7 @@
         <v>7</v>
       </c>
       <c r="D1077">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1077" t="s">
         <v>8</v>
@@ -22377,7 +22377,7 @@
         <v>7</v>
       </c>
       <c r="D1078">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1078" t="s">
         <v>8</v>
@@ -22394,7 +22394,7 @@
         <v>7</v>
       </c>
       <c r="D1079">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1079" t="s">
         <v>8</v>
@@ -22411,7 +22411,7 @@
         <v>7</v>
       </c>
       <c r="D1080">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1080" t="s">
         <v>8</v>
@@ -22428,7 +22428,7 @@
         <v>7</v>
       </c>
       <c r="D1081">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1081" t="s">
         <v>8</v>
@@ -22445,7 +22445,7 @@
         <v>7</v>
       </c>
       <c r="D1082">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1082" t="s">
         <v>8</v>
@@ -22479,7 +22479,7 @@
         <v>7</v>
       </c>
       <c r="D1084">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1084" t="s">
         <v>8</v>
@@ -22496,7 +22496,7 @@
         <v>7</v>
       </c>
       <c r="D1085">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1085" t="s">
         <v>8</v>
@@ -22530,7 +22530,7 @@
         <v>7</v>
       </c>
       <c r="D1087">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1087" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>7</v>
       </c>
       <c r="D1088">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1088" t="s">
         <v>8</v>
@@ -22564,7 +22564,7 @@
         <v>7</v>
       </c>
       <c r="D1089">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1089" t="s">
         <v>8</v>
@@ -22581,7 +22581,7 @@
         <v>7</v>
       </c>
       <c r="D1090">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1090" t="s">
         <v>8</v>
@@ -22598,7 +22598,7 @@
         <v>7</v>
       </c>
       <c r="D1091">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1091" t="s">
         <v>8</v>
@@ -22632,7 +22632,7 @@
         <v>7</v>
       </c>
       <c r="D1093">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1093" t="s">
         <v>8</v>
@@ -22649,7 +22649,7 @@
         <v>7</v>
       </c>
       <c r="D1094">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1094" t="s">
         <v>8</v>
@@ -22666,7 +22666,7 @@
         <v>7</v>
       </c>
       <c r="D1095">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1095" t="s">
         <v>8</v>
@@ -22683,7 +22683,7 @@
         <v>7</v>
       </c>
       <c r="D1096">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1096" t="s">
         <v>8</v>
@@ -22700,7 +22700,7 @@
         <v>7</v>
       </c>
       <c r="D1097">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1097" t="s">
         <v>8</v>
@@ -22717,7 +22717,7 @@
         <v>7</v>
       </c>
       <c r="D1098">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1098" t="s">
         <v>8</v>
@@ -22734,7 +22734,7 @@
         <v>7</v>
       </c>
       <c r="D1099">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1099" t="s">
         <v>8</v>
@@ -22751,7 +22751,7 @@
         <v>7</v>
       </c>
       <c r="D1100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1100" t="s">
         <v>8</v>
@@ -22768,7 +22768,7 @@
         <v>7</v>
       </c>
       <c r="D1101">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1101" t="s">
         <v>8</v>
@@ -22815,7 +22815,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>141</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -22829,7 +22829,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -22843,7 +22843,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>129</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -22857,7 +22857,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>161</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -22871,7 +22871,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -22885,7 +22885,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -22899,7 +22899,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -22913,7 +22913,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>62</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -22927,7 +22927,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>67</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -22941,7 +22941,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>71</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -22969,7 +22969,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>79</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -22983,7 +22983,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>92</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -22997,7 +22997,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>74</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23011,7 +23011,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>68</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23025,7 +23025,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>124</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -23039,7 +23039,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>71</v>
+        <v>452</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23053,7 +23053,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>70</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23067,7 +23067,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>67</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -23081,7 +23081,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>106</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23095,7 +23095,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>73</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -23109,7 +23109,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>72</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23123,7 +23123,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>72</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23137,7 +23137,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>81</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -23151,7 +23151,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>71</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23165,7 +23165,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>71</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23179,7 +23179,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>68</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -23193,7 +23193,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>70</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23207,7 +23207,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>71</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -23221,7 +23221,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>93</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23235,7 +23235,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>93</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23249,7 +23249,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23263,7 +23263,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -23277,7 +23277,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -23291,7 +23291,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23305,7 +23305,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23319,7 +23319,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -23333,7 +23333,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -23347,7 +23347,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23361,7 +23361,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23375,7 +23375,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -23389,7 +23389,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -23403,7 +23403,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23417,7 +23417,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>144</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23431,7 +23431,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>115</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -23445,7 +23445,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>119</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23459,7 +23459,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23473,7 +23473,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23487,7 +23487,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23501,7 +23501,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23515,7 +23515,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23529,7 +23529,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -23557,7 +23557,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>78</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23571,7 +23571,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>82</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23585,7 +23585,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>80</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -23599,7 +23599,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>89</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -23613,7 +23613,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -23627,7 +23627,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -23641,7 +23641,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -23655,7 +23655,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -23683,7 +23683,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -23697,7 +23697,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -23711,7 +23711,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -23725,7 +23725,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -23739,7 +23739,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -23753,7 +23753,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -23767,7 +23767,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -23781,7 +23781,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>65</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -23795,7 +23795,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>72</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -23809,7 +23809,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>69</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -23823,7 +23823,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>70</v>
+        <v>123</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -23837,7 +23837,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>66</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -23851,7 +23851,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>63</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -23865,7 +23865,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>67</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -23879,7 +23879,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>67</v>
+        <v>123</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -23893,7 +23893,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>68</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -23907,7 +23907,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>68</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -23921,7 +23921,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>65</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -23935,7 +23935,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>68</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -23949,7 +23949,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>64</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -23963,7 +23963,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>66</v>
+        <v>155</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -23977,7 +23977,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>67</v>
+        <v>506</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -23991,7 +23991,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>67</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -24005,7 +24005,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>68</v>
+        <v>914</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -24019,7 +24019,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>67</v>
+        <v>294</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -24033,7 +24033,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>67</v>
+        <v>164</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -24047,7 +24047,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -24061,7 +24061,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>67</v>
+        <v>83</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -24075,7 +24075,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>69</v>
+        <v>108</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -24089,7 +24089,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>67</v>
+        <v>83</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -24103,7 +24103,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -24117,7 +24117,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -24131,7 +24131,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -24145,7 +24145,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -24159,7 +24159,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>71</v>
+        <v>92</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -24173,7 +24173,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>66</v>
+        <v>85</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -24187,7 +24187,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -24201,7 +24201,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -24215,7 +24215,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -24229,7 +24229,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -24243,7 +24243,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -24257,7 +24257,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -24271,7 +24271,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -24285,7 +24285,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -24299,7 +24299,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -24313,7 +24313,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>64</v>
+        <v>78</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -24327,7 +24327,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -24341,7 +24341,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
